--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Curtis Garage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2BE4B37-B15D-4A09-B74C-5972B809CD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D31405-AE16-464C-BA1E-75517AB27DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="1065" windowWidth="24720" windowHeight="14235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Curtis Garage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D31405-AE16-464C-BA1E-75517AB27DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ADA714-455A-4C49-845A-7B684F7F6E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9075,10 +9075,10 @@
         <v>29</v>
       </c>
       <c r="G272" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H272" s="2">
-        <v>0</v>
+        <v>4.5486111111111109E-3</v>
       </c>
       <c r="I272" s="1">
         <v>46083.725462962961</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ADA714-455A-4C49-845A-7B684F7F6E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DA8A22-392F-4A89-8264-D9EE5ED63BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DA8A22-392F-4A89-8264-D9EE5ED63BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B575569F-9F75-4B8C-8101-70119209B432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="56">
   <si>
     <t>Company Name</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>Walker Sims</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -9379,94 +9382,411 @@
       </c>
     </row>
     <row r="282" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H282" s="2"/>
-      <c r="I282" s="1"/>
+      <c r="B282" t="s">
+        <v>35</v>
+      </c>
+      <c r="C282">
+        <v>2067</v>
+      </c>
+      <c r="D282" t="s">
+        <v>51</v>
+      </c>
+      <c r="E282" t="s">
+        <v>37</v>
+      </c>
+      <c r="F282" t="s">
+        <v>55</v>
+      </c>
+      <c r="G282" t="s">
+        <v>13</v>
+      </c>
+      <c r="H282" s="2">
+        <v>0</v>
+      </c>
+      <c r="I282" s="1">
+        <v>46118.757986111108</v>
+      </c>
+      <c r="J282">
+        <v>1</v>
+      </c>
+      <c r="K282" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="283" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H283" s="2"/>
-      <c r="I283" s="1"/>
+      <c r="B283" t="s">
+        <v>35</v>
+      </c>
+      <c r="C283">
+        <v>1125</v>
+      </c>
+      <c r="D283" t="s">
+        <v>39</v>
+      </c>
+      <c r="E283" t="s">
+        <v>37</v>
+      </c>
+      <c r="F283" t="s">
+        <v>55</v>
+      </c>
+      <c r="G283" t="s">
+        <v>13</v>
+      </c>
+      <c r="H283" s="2">
+        <v>0</v>
+      </c>
+      <c r="I283" s="1">
+        <v>46118.758680555555</v>
+      </c>
+      <c r="J283">
+        <v>1</v>
+      </c>
+      <c r="K283" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="284" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H284" s="2"/>
-      <c r="I284" s="1"/>
+      <c r="B284" t="s">
+        <v>35</v>
+      </c>
+      <c r="C284">
+        <v>1126</v>
+      </c>
+      <c r="D284" t="s">
+        <v>41</v>
+      </c>
+      <c r="E284" t="s">
+        <v>37</v>
+      </c>
+      <c r="F284" t="s">
+        <v>55</v>
+      </c>
+      <c r="G284" t="s">
+        <v>10</v>
+      </c>
+      <c r="H284" s="2">
+        <v>6.2615740740740739E-3</v>
+      </c>
+      <c r="I284" s="1">
+        <v>46118.758680555555</v>
+      </c>
+      <c r="J284">
+        <v>1</v>
+      </c>
+      <c r="K284" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="285" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H285" s="2"/>
-      <c r="I285" s="1"/>
+      <c r="B285" t="s">
+        <v>35</v>
+      </c>
+      <c r="C285">
+        <v>1128</v>
+      </c>
+      <c r="D285" t="s">
+        <v>42</v>
+      </c>
+      <c r="E285" t="s">
+        <v>37</v>
+      </c>
+      <c r="F285" t="s">
+        <v>55</v>
+      </c>
+      <c r="G285" t="s">
+        <v>12</v>
+      </c>
+      <c r="H285" s="2">
+        <v>3.5648148148148149E-3</v>
+      </c>
+      <c r="I285" s="1">
+        <v>46118.759375000001</v>
+      </c>
+      <c r="J285">
+        <v>1</v>
+      </c>
+      <c r="K285" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="286" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H286" s="2"/>
       <c r="I286" s="1"/>
+      <c r="K286" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="287" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H287" s="2"/>
-      <c r="I287" s="1"/>
+      <c r="B287" t="s">
+        <v>35</v>
+      </c>
+      <c r="C287">
+        <v>914</v>
+      </c>
+      <c r="D287" t="s">
+        <v>43</v>
+      </c>
+      <c r="E287" t="s">
+        <v>37</v>
+      </c>
+      <c r="F287" t="s">
+        <v>55</v>
+      </c>
+      <c r="G287" t="s">
+        <v>10</v>
+      </c>
+      <c r="H287" s="2">
+        <v>1.7002314814814814E-2</v>
+      </c>
+      <c r="I287" s="1">
+        <v>46118.759375000001</v>
+      </c>
+      <c r="J287">
+        <v>1</v>
+      </c>
+      <c r="K287" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="288" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H288" s="2"/>
-      <c r="I288" s="1"/>
-    </row>
-    <row r="289" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H289" s="2"/>
-      <c r="I289" s="1"/>
-    </row>
-    <row r="290" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H290" s="2"/>
-      <c r="I290" s="1"/>
-    </row>
-    <row r="291" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H291" s="2"/>
-      <c r="I291" s="1"/>
-    </row>
-    <row r="292" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B288" t="s">
+        <v>35</v>
+      </c>
+      <c r="C288">
+        <v>1130</v>
+      </c>
+      <c r="D288" t="s">
+        <v>44</v>
+      </c>
+      <c r="E288" t="s">
+        <v>37</v>
+      </c>
+      <c r="F288" t="s">
+        <v>55</v>
+      </c>
+      <c r="G288" t="s">
+        <v>13</v>
+      </c>
+      <c r="H288" s="2">
+        <v>0</v>
+      </c>
+      <c r="I288" s="1">
+        <v>46118.760069444441</v>
+      </c>
+      <c r="J288">
+        <v>1</v>
+      </c>
+      <c r="K288" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="289" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B289" t="s">
+        <v>35</v>
+      </c>
+      <c r="C289">
+        <v>1129</v>
+      </c>
+      <c r="D289" t="s">
+        <v>45</v>
+      </c>
+      <c r="E289" t="s">
+        <v>37</v>
+      </c>
+      <c r="F289" t="s">
+        <v>55</v>
+      </c>
+      <c r="G289" t="s">
+        <v>10</v>
+      </c>
+      <c r="H289" s="2">
+        <v>9.5949074074074079E-3</v>
+      </c>
+      <c r="I289" s="1">
+        <v>46118.760763888888</v>
+      </c>
+      <c r="J289">
+        <v>1</v>
+      </c>
+      <c r="K289" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="290" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B290" t="s">
+        <v>35</v>
+      </c>
+      <c r="C290">
+        <v>771</v>
+      </c>
+      <c r="D290" t="s">
+        <v>46</v>
+      </c>
+      <c r="E290" t="s">
+        <v>37</v>
+      </c>
+      <c r="F290" t="s">
+        <v>55</v>
+      </c>
+      <c r="G290" t="s">
+        <v>10</v>
+      </c>
+      <c r="H290" s="2">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="I290" s="1">
+        <v>46118.760763888888</v>
+      </c>
+      <c r="J290">
+        <v>1</v>
+      </c>
+      <c r="K290" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="291" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B291" t="s">
+        <v>35</v>
+      </c>
+      <c r="C291">
+        <v>2268</v>
+      </c>
+      <c r="D291" t="s">
+        <v>37</v>
+      </c>
+      <c r="E291" t="s">
+        <v>37</v>
+      </c>
+      <c r="F291" t="s">
+        <v>55</v>
+      </c>
+      <c r="G291" t="s">
+        <v>12</v>
+      </c>
+      <c r="H291" s="2">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="I291" s="1">
+        <v>46118.761458333334</v>
+      </c>
+      <c r="J291">
+        <v>1</v>
+      </c>
+      <c r="K291" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="292" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H292" s="2"/>
       <c r="I292" s="1"/>
-    </row>
-    <row r="293" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H293" s="2"/>
-      <c r="I293" s="1"/>
-    </row>
-    <row r="294" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H294" s="2"/>
-      <c r="I294" s="1"/>
-    </row>
-    <row r="295" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K292" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="293" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B293" t="s">
+        <v>35</v>
+      </c>
+      <c r="C293">
+        <v>4661</v>
+      </c>
+      <c r="D293" t="s">
+        <v>54</v>
+      </c>
+      <c r="E293" t="s">
+        <v>37</v>
+      </c>
+      <c r="F293" t="s">
+        <v>55</v>
+      </c>
+      <c r="G293" t="s">
+        <v>10</v>
+      </c>
+      <c r="H293" s="2">
+        <v>9.0046296296296298E-3</v>
+      </c>
+      <c r="I293" s="1">
+        <v>46118.762152777781</v>
+      </c>
+      <c r="J293">
+        <v>1</v>
+      </c>
+      <c r="K293" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="294" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B294" t="s">
+        <v>35</v>
+      </c>
+      <c r="C294">
+        <v>1132</v>
+      </c>
+      <c r="D294" t="s">
+        <v>47</v>
+      </c>
+      <c r="E294" t="s">
+        <v>37</v>
+      </c>
+      <c r="F294" t="s">
+        <v>55</v>
+      </c>
+      <c r="G294" t="s">
+        <v>12</v>
+      </c>
+      <c r="H294" s="2">
+        <v>5.2430555555555555E-3</v>
+      </c>
+      <c r="I294" s="1">
+        <v>46118.762152777781</v>
+      </c>
+      <c r="J294">
+        <v>0</v>
+      </c>
+      <c r="K294" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="295" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H295" s="2"/>
       <c r="I295" s="1"/>
-    </row>
-    <row r="296" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K295" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="296" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H296" s="2"/>
       <c r="I296" s="1"/>
     </row>
-    <row r="297" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H297" s="2"/>
       <c r="I297" s="1"/>
     </row>
-    <row r="298" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H298" s="2"/>
       <c r="I298" s="1"/>
     </row>
-    <row r="299" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H299" s="2"/>
       <c r="I299" s="1"/>
     </row>
-    <row r="300" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H300" s="2"/>
       <c r="I300" s="1"/>
     </row>
-    <row r="301" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H301" s="2"/>
       <c r="I301" s="1"/>
     </row>
-    <row r="302" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H302" s="2"/>
       <c r="I302" s="1"/>
     </row>
-    <row r="303" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H303" s="2"/>
       <c r="I303" s="1"/>
     </row>
-    <row r="304" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H304" s="2"/>
       <c r="I304" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B575569F-9F75-4B8C-8101-70119209B432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFC5B05-F9CE-44F8-BAC9-570521B28416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="56">
   <si>
     <t>Company Name</t>
   </si>
@@ -9407,7 +9407,7 @@
         <v>46118.757986111108</v>
       </c>
       <c r="J282">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K282" t="s">
         <v>11</v>
@@ -9430,51 +9430,26 @@
         <v>55</v>
       </c>
       <c r="G283" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H283" s="2">
-        <v>0</v>
+        <v>7.743055555555556E-3</v>
       </c>
       <c r="I283" s="1">
         <v>46118.758680555555</v>
       </c>
       <c r="J283">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K283" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="284" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B284" t="s">
-        <v>35</v>
-      </c>
-      <c r="C284">
-        <v>1126</v>
-      </c>
-      <c r="D284" t="s">
-        <v>41</v>
-      </c>
-      <c r="E284" t="s">
-        <v>37</v>
-      </c>
-      <c r="F284" t="s">
-        <v>55</v>
-      </c>
-      <c r="G284" t="s">
-        <v>10</v>
-      </c>
-      <c r="H284" s="2">
-        <v>6.2615740740740739E-3</v>
-      </c>
-      <c r="I284" s="1">
-        <v>46118.758680555555</v>
-      </c>
-      <c r="J284">
-        <v>1</v>
-      </c>
+      <c r="H284" s="2"/>
+      <c r="I284" s="1"/>
       <c r="K284" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="285" spans="2:11" x14ac:dyDescent="0.25">
@@ -9482,10 +9457,10 @@
         <v>35</v>
       </c>
       <c r="C285">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="D285" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E285" t="s">
         <v>37</v>
@@ -9494,13 +9469,13 @@
         <v>55</v>
       </c>
       <c r="G285" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H285" s="2">
-        <v>3.5648148148148149E-3</v>
+        <v>6.2615740740740739E-3</v>
       </c>
       <c r="I285" s="1">
-        <v>46118.759375000001</v>
+        <v>46118.758680555555</v>
       </c>
       <c r="J285">
         <v>1</v>
@@ -9510,42 +9485,42 @@
       </c>
     </row>
     <row r="286" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H286" s="2"/>
-      <c r="I286" s="1"/>
+      <c r="B286" t="s">
+        <v>35</v>
+      </c>
+      <c r="C286">
+        <v>1128</v>
+      </c>
+      <c r="D286" t="s">
+        <v>42</v>
+      </c>
+      <c r="E286" t="s">
+        <v>37</v>
+      </c>
+      <c r="F286" t="s">
+        <v>55</v>
+      </c>
+      <c r="G286" t="s">
+        <v>12</v>
+      </c>
+      <c r="H286" s="2">
+        <v>3.5648148148148149E-3</v>
+      </c>
+      <c r="I286" s="1">
+        <v>46118.759375000001</v>
+      </c>
+      <c r="J286">
+        <v>1</v>
+      </c>
       <c r="K286" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="287" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H287" s="2"/>
+      <c r="I287" s="1"/>
+      <c r="K287" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="287" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B287" t="s">
-        <v>35</v>
-      </c>
-      <c r="C287">
-        <v>914</v>
-      </c>
-      <c r="D287" t="s">
-        <v>43</v>
-      </c>
-      <c r="E287" t="s">
-        <v>37</v>
-      </c>
-      <c r="F287" t="s">
-        <v>55</v>
-      </c>
-      <c r="G287" t="s">
-        <v>10</v>
-      </c>
-      <c r="H287" s="2">
-        <v>1.7002314814814814E-2</v>
-      </c>
-      <c r="I287" s="1">
-        <v>46118.759375000001</v>
-      </c>
-      <c r="J287">
-        <v>1</v>
-      </c>
-      <c r="K287" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="288" spans="2:11" x14ac:dyDescent="0.25">
@@ -9553,10 +9528,10 @@
         <v>35</v>
       </c>
       <c r="C288">
-        <v>1130</v>
+        <v>914</v>
       </c>
       <c r="D288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E288" t="s">
         <v>37</v>
@@ -9565,13 +9540,13 @@
         <v>55</v>
       </c>
       <c r="G288" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H288" s="2">
-        <v>0</v>
+        <v>1.7002314814814814E-2</v>
       </c>
       <c r="I288" s="1">
-        <v>46118.760069444441</v>
+        <v>46118.759375000001</v>
       </c>
       <c r="J288">
         <v>1</v>
@@ -9585,10 +9560,10 @@
         <v>35</v>
       </c>
       <c r="C289">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D289" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E289" t="s">
         <v>37</v>
@@ -9597,16 +9572,16 @@
         <v>55</v>
       </c>
       <c r="G289" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H289" s="2">
-        <v>9.5949074074074079E-3</v>
+        <v>0</v>
       </c>
       <c r="I289" s="1">
-        <v>46118.760763888888</v>
+        <v>46118.760069444441</v>
       </c>
       <c r="J289">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K289" t="s">
         <v>11</v>
@@ -9617,10 +9592,10 @@
         <v>35</v>
       </c>
       <c r="C290">
-        <v>771</v>
+        <v>1129</v>
       </c>
       <c r="D290" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E290" t="s">
         <v>37</v>
@@ -9632,7 +9607,7 @@
         <v>10</v>
       </c>
       <c r="H290" s="2">
-        <v>6.9444444444444441E-3</v>
+        <v>9.5949074074074079E-3</v>
       </c>
       <c r="I290" s="1">
         <v>46118.760763888888</v>
@@ -9649,10 +9624,10 @@
         <v>35</v>
       </c>
       <c r="C291">
-        <v>2268</v>
+        <v>771</v>
       </c>
       <c r="D291" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E291" t="s">
         <v>37</v>
@@ -9661,13 +9636,13 @@
         <v>55</v>
       </c>
       <c r="G291" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H291" s="2">
-        <v>1.1458333333333333E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="I291" s="1">
-        <v>46118.761458333334</v>
+        <v>46118.760763888888</v>
       </c>
       <c r="J291">
         <v>1</v>
@@ -9677,42 +9652,42 @@
       </c>
     </row>
     <row r="292" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H292" s="2"/>
-      <c r="I292" s="1"/>
+      <c r="B292" t="s">
+        <v>35</v>
+      </c>
+      <c r="C292">
+        <v>2268</v>
+      </c>
+      <c r="D292" t="s">
+        <v>37</v>
+      </c>
+      <c r="E292" t="s">
+        <v>37</v>
+      </c>
+      <c r="F292" t="s">
+        <v>55</v>
+      </c>
+      <c r="G292" t="s">
+        <v>12</v>
+      </c>
+      <c r="H292" s="2">
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="I292" s="1">
+        <v>46118.761458333334</v>
+      </c>
+      <c r="J292">
+        <v>1</v>
+      </c>
       <c r="K292" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="293" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H293" s="2"/>
+      <c r="I293" s="1"/>
+      <c r="K293" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="293" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B293" t="s">
-        <v>35</v>
-      </c>
-      <c r="C293">
-        <v>4661</v>
-      </c>
-      <c r="D293" t="s">
-        <v>54</v>
-      </c>
-      <c r="E293" t="s">
-        <v>37</v>
-      </c>
-      <c r="F293" t="s">
-        <v>55</v>
-      </c>
-      <c r="G293" t="s">
-        <v>10</v>
-      </c>
-      <c r="H293" s="2">
-        <v>9.0046296296296298E-3</v>
-      </c>
-      <c r="I293" s="1">
-        <v>46118.762152777781</v>
-      </c>
-      <c r="J293">
-        <v>1</v>
-      </c>
-      <c r="K293" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="294" spans="2:11" x14ac:dyDescent="0.25">
@@ -9720,10 +9695,10 @@
         <v>35</v>
       </c>
       <c r="C294">
-        <v>1132</v>
+        <v>4661</v>
       </c>
       <c r="D294" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E294" t="s">
         <v>37</v>
@@ -9732,31 +9707,59 @@
         <v>55</v>
       </c>
       <c r="G294" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H294" s="2">
-        <v>5.2430555555555555E-3</v>
+        <v>9.0046296296296298E-3</v>
       </c>
       <c r="I294" s="1">
         <v>46118.762152777781</v>
       </c>
       <c r="J294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K294" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="295" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H295" s="2"/>
-      <c r="I295" s="1"/>
+      <c r="B295" t="s">
+        <v>35</v>
+      </c>
+      <c r="C295">
+        <v>1132</v>
+      </c>
+      <c r="D295" t="s">
+        <v>47</v>
+      </c>
+      <c r="E295" t="s">
+        <v>37</v>
+      </c>
+      <c r="F295" t="s">
+        <v>55</v>
+      </c>
+      <c r="G295" t="s">
+        <v>12</v>
+      </c>
+      <c r="H295" s="2">
+        <v>5.2430555555555555E-3</v>
+      </c>
+      <c r="I295" s="1">
+        <v>46118.762152777781</v>
+      </c>
+      <c r="J295">
+        <v>0</v>
+      </c>
       <c r="K295" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="296" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H296" s="2"/>
       <c r="I296" s="1"/>
+      <c r="K296" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="297" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H297" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFC5B05-F9CE-44F8-BAC9-570521B28416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCC428B-3A45-4C51-AC6D-BCE3527D64B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -86,46 +86,10 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
-  </si>
-  <si>
-    <t>Vehicle Inspections</t>
-  </si>
-  <si>
     <t>Winter Weather</t>
   </si>
   <si>
     <t>December Driving Edition</t>
-  </si>
-  <si>
-    <t>Rules for Safe Driving</t>
-  </si>
-  <si>
-    <t>Space Management-Big 5</t>
-  </si>
-  <si>
-    <t>Distracted Driving</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Alert Driving</t>
-  </si>
-  <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>3 points of contact</t>
-  </si>
-  <si>
-    <t>Vehicle &amp; Roadside Inspections CMV</t>
-  </si>
-  <si>
-    <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Safe RR Crossing</t>
   </si>
   <si>
     <t>Drowsy Driving</t>
@@ -137,13 +101,13 @@
     <t>Mark Complete</t>
   </si>
   <si>
-    <t>Fire Extinguisher Training for CDL</t>
-  </si>
-  <si>
     <t>Alert Driving: Big Three</t>
   </si>
   <si>
     <t>Camera Event Management Orientation for Drivers</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Curtis Garage and Wrecker</t>
@@ -197,16 +161,52 @@
     <t>Cole Curtis</t>
   </si>
   <si>
+    <t>Vehicle Inspections</t>
+  </si>
+  <si>
+    <t>Space Management-Big 5</t>
+  </si>
+  <si>
+    <t>Alert Driving</t>
+  </si>
+  <si>
+    <t>Speed Management</t>
+  </si>
+  <si>
+    <t>Rules for Safe Driving</t>
+  </si>
+  <si>
+    <t>Distracted Driving</t>
+  </si>
+  <si>
+    <t>Safe RR Crossing</t>
+  </si>
+  <si>
+    <t>3 points of contact</t>
+  </si>
+  <si>
     <t>Micro-Learn Speed</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Micro-Learn Space Mangement</t>
   </si>
   <si>
+    <t>Work Zone Safety</t>
+  </si>
+  <si>
+    <t>Dangers of Aggressive Driving for CMV Drivers</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
+  </si>
+  <si>
     <t>Walker Sims</t>
   </si>
   <si>
-    <t>Space Management for Commercial Vehicles</t>
+    <t>Vehicle &amp; Roadside Inspections CMV</t>
   </si>
 </sst>
 </file>
@@ -629,19 +629,19 @@
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>1124</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -661,19 +661,19 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>1125</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
@@ -693,16 +693,16 @@
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>1127</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -722,19 +722,19 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>1126</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -754,19 +754,19 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>1128</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
@@ -786,19 +786,19 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>914</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
@@ -818,19 +818,19 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>1130</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
@@ -850,19 +850,19 @@
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C9">
         <v>1129</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
@@ -882,19 +882,19 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C10">
         <v>771</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -914,16 +914,16 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C11">
         <v>1626</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -943,19 +943,19 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C12">
         <v>1132</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G12" t="s">
         <v>10</v>
@@ -975,19 +975,19 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C13">
         <v>1124</v>
       </c>
       <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
         <v>36</v>
-      </c>
-      <c r="E13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
       </c>
       <c r="G13" t="s">
         <v>10</v>
@@ -1007,19 +1007,19 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C14">
         <v>1125</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
         <v>10</v>
@@ -1039,19 +1039,19 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>1126</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
         <v>10</v>
@@ -1071,19 +1071,19 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C16">
         <v>1128</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
         <v>10</v>
@@ -1103,19 +1103,19 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C17">
         <v>914</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -1135,19 +1135,19 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>1130</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
         <v>10</v>
@@ -1167,19 +1167,19 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C19">
         <v>1129</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -1201,24 +1201,24 @@
       <c r="H20" s="2"/>
       <c r="I20" s="1"/>
       <c r="K20" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>771</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
         <v>10</v>
@@ -1238,19 +1238,19 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C22">
         <v>1132</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s">
         <v>10</v>
@@ -1270,19 +1270,19 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C23">
         <v>1124</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
         <v>37</v>
-      </c>
-      <c r="F23" t="s">
-        <v>49</v>
       </c>
       <c r="G23" t="s">
         <v>10</v>
@@ -1302,19 +1302,19 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C24">
         <v>1125</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
         <v>37</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
       </c>
       <c r="G24" t="s">
         <v>10</v>
@@ -1334,19 +1334,19 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C25">
         <v>1126</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
         <v>37</v>
-      </c>
-      <c r="F25" t="s">
-        <v>49</v>
       </c>
       <c r="G25" t="s">
         <v>10</v>
@@ -1366,19 +1366,19 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C26">
         <v>1128</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
         <v>37</v>
-      </c>
-      <c r="F26" t="s">
-        <v>49</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -1398,19 +1398,19 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C27">
         <v>914</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
         <v>37</v>
-      </c>
-      <c r="F27" t="s">
-        <v>49</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1430,19 +1430,19 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C28">
         <v>1130</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
         <v>37</v>
-      </c>
-      <c r="F28" t="s">
-        <v>49</v>
       </c>
       <c r="G28" t="s">
         <v>10</v>
@@ -1462,19 +1462,19 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C29">
         <v>1129</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
         <v>37</v>
-      </c>
-      <c r="F29" t="s">
-        <v>49</v>
       </c>
       <c r="G29" t="s">
         <v>12</v>
@@ -1496,24 +1496,24 @@
       <c r="H30" s="2"/>
       <c r="I30" s="1"/>
       <c r="K30" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C31">
         <v>771</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
         <v>37</v>
-      </c>
-      <c r="F31" t="s">
-        <v>49</v>
       </c>
       <c r="G31" t="s">
         <v>10</v>
@@ -1533,19 +1533,19 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C32">
         <v>1132</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
         <v>37</v>
-      </c>
-      <c r="F32" t="s">
-        <v>49</v>
       </c>
       <c r="G32" t="s">
         <v>10</v>
@@ -1565,19 +1565,19 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C33">
         <v>1124</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
@@ -1597,19 +1597,19 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C34">
         <v>2067</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -1629,19 +1629,19 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C35">
         <v>1125</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -1661,19 +1661,19 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C36">
         <v>1126</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F36" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G36" t="s">
         <v>10</v>
@@ -1693,19 +1693,19 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C37">
         <v>1128</v>
       </c>
       <c r="D37" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F37" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G37" t="s">
         <v>10</v>
@@ -1725,19 +1725,19 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C38">
         <v>914</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G38" t="s">
         <v>10</v>
@@ -1757,19 +1757,19 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C39">
         <v>1130</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E39" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G39" t="s">
         <v>12</v>
@@ -1791,24 +1791,24 @@
       <c r="H40" s="2"/>
       <c r="I40" s="1"/>
       <c r="K40" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C41">
         <v>1129</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E41" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G41" t="s">
         <v>13</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C42">
         <v>771</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E42" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G42" t="s">
         <v>10</v>
@@ -1860,19 +1860,19 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C43">
         <v>1132</v>
       </c>
       <c r="D43" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F43" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G43" t="s">
         <v>12</v>
@@ -1894,24 +1894,24 @@
       <c r="H44" s="2"/>
       <c r="I44" s="1"/>
       <c r="K44" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C45">
         <v>1124</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G45" t="s">
         <v>10</v>
@@ -1931,19 +1931,19 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C46">
         <v>2067</v>
       </c>
       <c r="D46" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E46" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G46" t="s">
         <v>10</v>
@@ -1963,19 +1963,19 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C47">
         <v>1125</v>
       </c>
       <c r="D47" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E47" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G47" t="s">
         <v>10</v>
@@ -1995,19 +1995,19 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C48">
         <v>1130</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E48" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G48" t="s">
         <v>10</v>
@@ -2027,19 +2027,19 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C49">
         <v>1129</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E49" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G49" t="s">
         <v>10</v>
@@ -2059,19 +2059,19 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C50">
         <v>1132</v>
       </c>
       <c r="D50" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G50" t="s">
         <v>10</v>
@@ -2091,19 +2091,19 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C51">
         <v>2268</v>
       </c>
       <c r="D51" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E51" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2123,19 +2123,19 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C52">
         <v>1130</v>
       </c>
       <c r="D52" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G52" t="s">
         <v>12</v>
@@ -2157,24 +2157,24 @@
       <c r="H53" s="2"/>
       <c r="I53" s="1"/>
       <c r="K53" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C54">
         <v>1130</v>
       </c>
       <c r="D54" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E54" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F54" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G54" t="s">
         <v>10</v>
@@ -2194,19 +2194,19 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C55">
         <v>1130</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G55" t="s">
         <v>14</v>
@@ -2228,24 +2228,24 @@
       <c r="H56" s="2"/>
       <c r="I56" s="1"/>
       <c r="K56" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C57">
         <v>1124</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G57" t="s">
         <v>10</v>
@@ -2265,19 +2265,19 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C58">
         <v>2067</v>
       </c>
       <c r="D58" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E58" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G58" t="s">
         <v>10</v>
@@ -2297,19 +2297,19 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C59">
         <v>1125</v>
       </c>
       <c r="D59" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E59" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G59" t="s">
         <v>10</v>
@@ -2329,19 +2329,19 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C60">
         <v>1126</v>
       </c>
       <c r="D60" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G60" t="s">
         <v>10</v>
@@ -2361,19 +2361,19 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C61">
         <v>1128</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E61" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G61" t="s">
         <v>10</v>
@@ -2393,19 +2393,19 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C62">
         <v>914</v>
       </c>
       <c r="D62" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G62" t="s">
         <v>10</v>
@@ -2425,19 +2425,19 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C63">
         <v>1130</v>
       </c>
       <c r="D63" t="s">
+        <v>32</v>
+      </c>
+      <c r="E63" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" t="s">
         <v>44</v>
-      </c>
-      <c r="E63" t="s">
-        <v>37</v>
-      </c>
-      <c r="F63" t="s">
-        <v>19</v>
       </c>
       <c r="G63" t="s">
         <v>10</v>
@@ -2457,19 +2457,19 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C64">
         <v>1129</v>
       </c>
       <c r="D64" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E64" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F64" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G64" t="s">
         <v>10</v>
@@ -2489,19 +2489,19 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C65">
         <v>771</v>
       </c>
       <c r="D65" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E65" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G65" t="s">
         <v>10</v>
@@ -2521,19 +2521,19 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C66">
         <v>2268</v>
       </c>
       <c r="D66" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F66" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2553,19 +2553,19 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C67">
         <v>1132</v>
       </c>
       <c r="D67" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E67" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F67" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G67" t="s">
         <v>10</v>
@@ -2585,19 +2585,19 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C68">
         <v>771</v>
       </c>
       <c r="D68" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E68" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F68" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G68" t="s">
         <v>10</v>
@@ -2617,19 +2617,19 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C69">
         <v>771</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G69" t="s">
         <v>10</v>
@@ -2649,19 +2649,19 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C70">
         <v>771</v>
       </c>
       <c r="D70" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E70" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F70" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G70" t="s">
         <v>10</v>
@@ -2681,19 +2681,19 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C71">
         <v>1128</v>
       </c>
       <c r="D71" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E71" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F71" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G71" t="s">
         <v>10</v>
@@ -2713,19 +2713,19 @@
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C72">
         <v>1128</v>
       </c>
       <c r="D72" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E72" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F72" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G72" t="s">
         <v>10</v>
@@ -2745,19 +2745,19 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C73">
         <v>1128</v>
       </c>
       <c r="D73" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" t="s">
         <v>42</v>
-      </c>
-      <c r="E73" t="s">
-        <v>37</v>
-      </c>
-      <c r="F73" t="s">
-        <v>23</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2777,19 +2777,19 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C74">
         <v>1124</v>
       </c>
       <c r="D74" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E74" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F74" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2809,19 +2809,19 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C75">
         <v>2067</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E75" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F75" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G75" t="s">
         <v>12</v>
@@ -2843,24 +2843,24 @@
       <c r="H76" s="2"/>
       <c r="I76" s="1"/>
       <c r="K76" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C77">
         <v>1125</v>
       </c>
       <c r="D77" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E77" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G77" t="s">
         <v>10</v>
@@ -2880,19 +2880,19 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C78">
         <v>1126</v>
       </c>
       <c r="D78" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F78" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G78" t="s">
         <v>10</v>
@@ -2912,19 +2912,19 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C79">
         <v>1128</v>
       </c>
       <c r="D79" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E79" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F79" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G79" t="s">
         <v>10</v>
@@ -2944,19 +2944,19 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C80">
         <v>914</v>
       </c>
       <c r="D80" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E80" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F80" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G80" t="s">
         <v>10</v>
@@ -2976,19 +2976,19 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C81">
         <v>1130</v>
       </c>
       <c r="D81" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E81" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F81" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G81" t="s">
         <v>10</v>
@@ -3008,19 +3008,19 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C82">
         <v>1129</v>
       </c>
       <c r="D82" t="s">
+        <v>33</v>
+      </c>
+      <c r="E82" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" t="s">
         <v>45</v>
-      </c>
-      <c r="E82" t="s">
-        <v>37</v>
-      </c>
-      <c r="F82" t="s">
-        <v>21</v>
       </c>
       <c r="G82" t="s">
         <v>10</v>
@@ -3040,19 +3040,19 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C83">
         <v>771</v>
       </c>
       <c r="D83" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E83" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G83" t="s">
         <v>10</v>
@@ -3072,19 +3072,19 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C84">
         <v>2268</v>
       </c>
       <c r="D84" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E84" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F84" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G84" t="s">
         <v>10</v>
@@ -3104,19 +3104,19 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C85">
         <v>1132</v>
       </c>
       <c r="D85" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E85" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F85" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G85" t="s">
         <v>10</v>
@@ -3136,19 +3136,19 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C86">
         <v>1124</v>
       </c>
       <c r="D86" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E86" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G86" t="s">
         <v>13</v>
@@ -3168,19 +3168,19 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C87">
         <v>1125</v>
       </c>
       <c r="D87" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E87" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F87" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G87" t="s">
         <v>10</v>
@@ -3200,19 +3200,19 @@
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C88">
         <v>1129</v>
       </c>
       <c r="D88" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E88" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F88" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G88" t="s">
         <v>13</v>
@@ -3232,19 +3232,19 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C89">
         <v>1124</v>
       </c>
       <c r="D89" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F89" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G89" t="s">
         <v>13</v>
@@ -3264,19 +3264,19 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C90">
         <v>1125</v>
       </c>
       <c r="D90" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E90" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G90" t="s">
         <v>10</v>
@@ -3296,19 +3296,19 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C91">
         <v>1129</v>
       </c>
       <c r="D91" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E91" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F91" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G91" t="s">
         <v>13</v>
@@ -3328,19 +3328,19 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C92">
         <v>1124</v>
       </c>
       <c r="D92" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E92" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G92" t="s">
         <v>13</v>
@@ -3360,19 +3360,19 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C93">
         <v>1125</v>
       </c>
       <c r="D93" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E93" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G93" t="s">
         <v>10</v>
@@ -3392,19 +3392,19 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C94">
         <v>1129</v>
       </c>
       <c r="D94" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E94" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F94" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G94" t="s">
         <v>13</v>
@@ -3424,19 +3424,19 @@
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C95">
         <v>1124</v>
       </c>
       <c r="D95" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F95" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G95" t="s">
         <v>10</v>
@@ -3456,19 +3456,19 @@
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C96">
         <v>1125</v>
       </c>
       <c r="D96" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E96" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F96" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G96" t="s">
         <v>10</v>
@@ -3488,19 +3488,19 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C97">
         <v>1129</v>
       </c>
       <c r="D97" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E97" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F97" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G97" t="s">
         <v>13</v>
@@ -3520,19 +3520,19 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C98">
         <v>1124</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E98" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F98" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G98" t="s">
         <v>10</v>
@@ -3552,19 +3552,19 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C99">
         <v>2067</v>
       </c>
       <c r="D99" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E99" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G99" t="s">
         <v>10</v>
@@ -3584,19 +3584,19 @@
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C100">
         <v>1125</v>
       </c>
       <c r="D100" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E100" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F100" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G100" t="s">
         <v>10</v>
@@ -3616,19 +3616,19 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C101">
         <v>1126</v>
       </c>
       <c r="D101" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E101" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F101" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G101" t="s">
         <v>10</v>
@@ -3648,19 +3648,19 @@
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C102">
         <v>1128</v>
       </c>
       <c r="D102" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E102" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F102" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G102" t="s">
         <v>10</v>
@@ -3680,19 +3680,19 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C103">
         <v>914</v>
       </c>
       <c r="D103" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F103" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G103" t="s">
         <v>10</v>
@@ -3712,19 +3712,19 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C104">
         <v>1130</v>
       </c>
       <c r="D104" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F104" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G104" t="s">
         <v>10</v>
@@ -3744,19 +3744,19 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C105">
         <v>1129</v>
       </c>
       <c r="D105" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E105" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F105" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G105" t="s">
         <v>10</v>
@@ -3776,19 +3776,19 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C106">
         <v>771</v>
       </c>
       <c r="D106" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E106" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G106" t="s">
         <v>10</v>
@@ -3808,19 +3808,19 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C107">
         <v>2268</v>
       </c>
       <c r="D107" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E107" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F107" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G107" t="s">
         <v>10</v>
@@ -3840,19 +3840,19 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C108">
         <v>1132</v>
       </c>
       <c r="D108" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E108" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F108" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G108" t="s">
         <v>10</v>
@@ -3872,19 +3872,19 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C109">
         <v>1124</v>
       </c>
       <c r="D109" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E109" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F109" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G109" t="s">
         <v>10</v>
@@ -3904,19 +3904,19 @@
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C110">
         <v>2067</v>
       </c>
       <c r="D110" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E110" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F110" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G110" t="s">
         <v>10</v>
@@ -3936,19 +3936,19 @@
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C111">
         <v>1125</v>
       </c>
       <c r="D111" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E111" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F111" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G111" t="s">
         <v>10</v>
@@ -3968,19 +3968,19 @@
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C112">
         <v>1126</v>
       </c>
       <c r="D112" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E112" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F112" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G112" t="s">
         <v>10</v>
@@ -4000,19 +4000,19 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C113">
         <v>1128</v>
       </c>
       <c r="D113" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E113" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F113" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G113" t="s">
         <v>10</v>
@@ -4032,19 +4032,19 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C114">
         <v>914</v>
       </c>
       <c r="D114" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E114" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G114" t="s">
         <v>10</v>
@@ -4064,19 +4064,19 @@
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C115">
         <v>1130</v>
       </c>
       <c r="D115" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E115" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G115" t="s">
         <v>10</v>
@@ -4096,19 +4096,19 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C116">
         <v>1129</v>
       </c>
       <c r="D116" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G116" t="s">
         <v>10</v>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C117">
         <v>771</v>
       </c>
       <c r="D117" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E117" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F117" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G117" t="s">
         <v>10</v>
@@ -4160,19 +4160,19 @@
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C118">
         <v>2268</v>
       </c>
       <c r="D118" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E118" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G118" t="s">
         <v>10</v>
@@ -4192,19 +4192,19 @@
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C119">
         <v>1132</v>
       </c>
       <c r="D119" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E119" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F119" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G119" t="s">
         <v>10</v>
@@ -4224,19 +4224,19 @@
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C120">
         <v>1124</v>
       </c>
       <c r="D120" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E120" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G120" t="s">
         <v>10</v>
@@ -4256,19 +4256,19 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C121">
         <v>2067</v>
       </c>
       <c r="D121" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E121" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F121" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G121" t="s">
         <v>10</v>
@@ -4288,19 +4288,19 @@
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C122">
         <v>1125</v>
       </c>
       <c r="D122" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E122" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F122" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G122" t="s">
         <v>10</v>
@@ -4320,19 +4320,19 @@
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C123">
         <v>1126</v>
       </c>
       <c r="D123" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E123" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F123" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G123" t="s">
         <v>10</v>
@@ -4352,19 +4352,19 @@
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C124">
         <v>1128</v>
       </c>
       <c r="D124" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E124" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F124" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G124" t="s">
         <v>10</v>
@@ -4384,19 +4384,19 @@
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C125">
         <v>914</v>
       </c>
       <c r="D125" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E125" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F125" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G125" t="s">
         <v>10</v>
@@ -4416,19 +4416,19 @@
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C126">
         <v>1130</v>
       </c>
       <c r="D126" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E126" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F126" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G126" t="s">
         <v>10</v>
@@ -4448,19 +4448,19 @@
     </row>
     <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C127">
         <v>1129</v>
       </c>
       <c r="D127" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F127" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G127" t="s">
         <v>10</v>
@@ -4480,19 +4480,19 @@
     </row>
     <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C128">
         <v>771</v>
       </c>
       <c r="D128" t="s">
+        <v>34</v>
+      </c>
+      <c r="E128" t="s">
+        <v>25</v>
+      </c>
+      <c r="F128" t="s">
         <v>46</v>
-      </c>
-      <c r="E128" t="s">
-        <v>37</v>
-      </c>
-      <c r="F128" t="s">
-        <v>28</v>
       </c>
       <c r="G128" t="s">
         <v>10</v>
@@ -4512,19 +4512,19 @@
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C129">
         <v>2268</v>
       </c>
       <c r="D129" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E129" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F129" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G129" t="s">
         <v>10</v>
@@ -4544,19 +4544,19 @@
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C130">
         <v>1132</v>
       </c>
       <c r="D130" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E130" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F130" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G130" t="s">
         <v>10</v>
@@ -4576,19 +4576,19 @@
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C131">
         <v>1124</v>
       </c>
       <c r="D131" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F131" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G131" t="s">
         <v>10</v>
@@ -4608,19 +4608,19 @@
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C132">
         <v>2067</v>
       </c>
       <c r="D132" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E132" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G132" t="s">
         <v>10</v>
@@ -4640,19 +4640,19 @@
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C133">
         <v>1125</v>
       </c>
       <c r="D133" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E133" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F133" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G133" t="s">
         <v>10</v>
@@ -4672,19 +4672,19 @@
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C134">
         <v>1126</v>
       </c>
       <c r="D134" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E134" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F134" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G134" t="s">
         <v>10</v>
@@ -4704,19 +4704,19 @@
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C135">
         <v>1128</v>
       </c>
       <c r="D135" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E135" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F135" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G135" t="s">
         <v>10</v>
@@ -4736,19 +4736,19 @@
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C136">
         <v>914</v>
       </c>
       <c r="D136" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E136" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F136" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G136" t="s">
         <v>10</v>
@@ -4768,19 +4768,19 @@
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C137">
         <v>1130</v>
       </c>
       <c r="D137" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E137" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G137" t="s">
         <v>10</v>
@@ -4800,19 +4800,19 @@
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C138">
         <v>1129</v>
       </c>
       <c r="D138" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E138" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F138" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G138" t="s">
         <v>10</v>
@@ -4832,19 +4832,19 @@
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C139">
         <v>771</v>
       </c>
       <c r="D139" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E139" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F139" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G139" t="s">
         <v>10</v>
@@ -4864,19 +4864,19 @@
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C140">
         <v>2268</v>
       </c>
       <c r="D140" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E140" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F140" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G140" t="s">
         <v>10</v>
@@ -4896,19 +4896,19 @@
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C141">
         <v>1132</v>
       </c>
       <c r="D141" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" t="s">
+        <v>25</v>
+      </c>
+      <c r="F141" t="s">
         <v>47</v>
-      </c>
-      <c r="E141" t="s">
-        <v>37</v>
-      </c>
-      <c r="F141" t="s">
-        <v>25</v>
       </c>
       <c r="G141" t="s">
         <v>10</v>
@@ -4928,19 +4928,19 @@
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C142">
         <v>1124</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E142" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F142" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G142" t="s">
         <v>10</v>
@@ -4960,19 +4960,19 @@
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C143">
         <v>2067</v>
       </c>
       <c r="D143" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E143" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F143" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G143" t="s">
         <v>10</v>
@@ -4992,19 +4992,19 @@
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C144">
         <v>1125</v>
       </c>
       <c r="D144" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E144" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F144" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G144" t="s">
         <v>10</v>
@@ -5024,19 +5024,19 @@
     </row>
     <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C145">
         <v>1126</v>
       </c>
       <c r="D145" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E145" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F145" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G145" t="s">
         <v>10</v>
@@ -5056,19 +5056,19 @@
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C146">
         <v>1128</v>
       </c>
       <c r="D146" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E146" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F146" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G146" t="s">
         <v>10</v>
@@ -5088,19 +5088,19 @@
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C147">
         <v>914</v>
       </c>
       <c r="D147" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E147" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F147" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G147" t="s">
         <v>10</v>
@@ -5120,19 +5120,19 @@
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C148">
         <v>1130</v>
       </c>
       <c r="D148" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E148" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F148" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G148" t="s">
         <v>10</v>
@@ -5152,19 +5152,19 @@
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C149">
         <v>1129</v>
       </c>
       <c r="D149" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E149" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F149" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G149" t="s">
         <v>10</v>
@@ -5184,19 +5184,19 @@
     </row>
     <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C150">
         <v>771</v>
       </c>
       <c r="D150" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E150" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F150" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G150" t="s">
         <v>10</v>
@@ -5216,19 +5216,19 @@
     </row>
     <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C151">
         <v>2268</v>
       </c>
       <c r="D151" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E151" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F151" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G151" t="s">
         <v>10</v>
@@ -5248,19 +5248,19 @@
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C152">
         <v>1132</v>
       </c>
       <c r="D152" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E152" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F152" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G152" t="s">
         <v>10</v>
@@ -5280,19 +5280,19 @@
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C153">
         <v>1124</v>
       </c>
       <c r="D153" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E153" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F153" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G153" t="s">
         <v>10</v>
@@ -5312,19 +5312,19 @@
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C154">
         <v>2067</v>
       </c>
       <c r="D154" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E154" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F154" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G154" t="s">
         <v>10</v>
@@ -5344,19 +5344,19 @@
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C155">
         <v>1125</v>
       </c>
       <c r="D155" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E155" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F155" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G155" t="s">
         <v>10</v>
@@ -5376,19 +5376,19 @@
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C156">
         <v>1126</v>
       </c>
       <c r="D156" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E156" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F156" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G156" t="s">
         <v>10</v>
@@ -5408,19 +5408,19 @@
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C157">
         <v>1128</v>
       </c>
       <c r="D157" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E157" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F157" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G157" t="s">
         <v>10</v>
@@ -5440,19 +5440,19 @@
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C158">
         <v>914</v>
       </c>
       <c r="D158" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E158" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F158" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G158" t="s">
         <v>10</v>
@@ -5472,19 +5472,19 @@
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C159">
         <v>1130</v>
       </c>
       <c r="D159" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E159" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F159" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G159" t="s">
         <v>10</v>
@@ -5504,19 +5504,19 @@
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C160">
         <v>1129</v>
       </c>
       <c r="D160" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E160" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F160" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G160" t="s">
         <v>10</v>
@@ -5536,19 +5536,19 @@
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C161">
         <v>771</v>
       </c>
       <c r="D161" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E161" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F161" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G161" t="s">
         <v>10</v>
@@ -5568,19 +5568,19 @@
     </row>
     <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C162">
         <v>2268</v>
       </c>
       <c r="D162" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E162" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F162" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G162" t="s">
         <v>10</v>
@@ -5600,19 +5600,19 @@
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C163">
         <v>1132</v>
       </c>
       <c r="D163" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E163" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F163" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G163" t="s">
         <v>10</v>
@@ -5632,19 +5632,19 @@
     </row>
     <row r="164" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C164">
         <v>2067</v>
       </c>
       <c r="D164" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F164" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G164" t="s">
         <v>10</v>
@@ -5664,19 +5664,19 @@
     </row>
     <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C165">
         <v>1125</v>
       </c>
       <c r="D165" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E165" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F165" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G165" t="s">
         <v>10</v>
@@ -5696,19 +5696,19 @@
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C166">
         <v>1126</v>
       </c>
       <c r="D166" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E166" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F166" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G166" t="s">
         <v>10</v>
@@ -5728,19 +5728,19 @@
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C167">
         <v>1128</v>
       </c>
       <c r="D167" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E167" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F167" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G167" t="s">
         <v>10</v>
@@ -5760,19 +5760,19 @@
     </row>
     <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C168">
         <v>914</v>
       </c>
       <c r="D168" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E168" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F168" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G168" t="s">
         <v>10</v>
@@ -5792,19 +5792,19 @@
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C169">
         <v>1130</v>
       </c>
       <c r="D169" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E169" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F169" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G169" t="s">
         <v>10</v>
@@ -5824,19 +5824,19 @@
     </row>
     <row r="170" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C170">
         <v>1129</v>
       </c>
       <c r="D170" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E170" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F170" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G170" t="s">
         <v>10</v>
@@ -5856,19 +5856,19 @@
     </row>
     <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C171">
         <v>771</v>
       </c>
       <c r="D171" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E171" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F171" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G171" t="s">
         <v>10</v>
@@ -5888,19 +5888,19 @@
     </row>
     <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C172">
         <v>2268</v>
       </c>
       <c r="D172" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E172" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F172" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G172" t="s">
         <v>10</v>
@@ -5920,19 +5920,19 @@
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C173">
         <v>1132</v>
       </c>
       <c r="D173" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E173" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F173" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G173" t="s">
         <v>10</v>
@@ -5952,19 +5952,19 @@
     </row>
     <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C174">
         <v>2067</v>
       </c>
       <c r="D174" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E174" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F174" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G174" t="s">
         <v>13</v>
@@ -5984,19 +5984,19 @@
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C175">
         <v>1125</v>
       </c>
       <c r="D175" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E175" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F175" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G175" t="s">
         <v>10</v>
@@ -6016,19 +6016,19 @@
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C176">
         <v>1126</v>
       </c>
       <c r="D176" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E176" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F176" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G176" t="s">
         <v>10</v>
@@ -6048,19 +6048,19 @@
     </row>
     <row r="177" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C177">
         <v>1128</v>
       </c>
       <c r="D177" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E177" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F177" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G177" t="s">
         <v>10</v>
@@ -6080,19 +6080,19 @@
     </row>
     <row r="178" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C178">
         <v>914</v>
       </c>
       <c r="D178" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E178" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F178" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G178" t="s">
         <v>10</v>
@@ -6112,19 +6112,19 @@
     </row>
     <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C179">
         <v>1130</v>
       </c>
       <c r="D179" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E179" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F179" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G179" t="s">
         <v>13</v>
@@ -6144,19 +6144,19 @@
     </row>
     <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C180">
         <v>1129</v>
       </c>
       <c r="D180" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E180" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F180" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G180" t="s">
         <v>10</v>
@@ -6176,19 +6176,19 @@
     </row>
     <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C181">
         <v>771</v>
       </c>
       <c r="D181" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E181" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F181" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G181" t="s">
         <v>10</v>
@@ -6208,19 +6208,19 @@
     </row>
     <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C182">
         <v>2268</v>
       </c>
       <c r="D182" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E182" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F182" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G182" t="s">
         <v>10</v>
@@ -6240,19 +6240,19 @@
     </row>
     <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C183">
         <v>1132</v>
       </c>
       <c r="D183" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E183" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F183" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G183" t="s">
         <v>10</v>
@@ -6272,19 +6272,19 @@
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C184">
         <v>2067</v>
       </c>
       <c r="D184" t="s">
+        <v>39</v>
+      </c>
+      <c r="E184" t="s">
+        <v>25</v>
+      </c>
+      <c r="F184" t="s">
         <v>51</v>
-      </c>
-      <c r="E184" t="s">
-        <v>37</v>
-      </c>
-      <c r="F184" t="s">
-        <v>22</v>
       </c>
       <c r="G184" t="s">
         <v>10</v>
@@ -6304,19 +6304,19 @@
     </row>
     <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C185">
         <v>1125</v>
       </c>
       <c r="D185" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E185" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F185" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G185" t="s">
         <v>10</v>
@@ -6336,19 +6336,19 @@
     </row>
     <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C186">
         <v>1126</v>
       </c>
       <c r="D186" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E186" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F186" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G186" t="s">
         <v>10</v>
@@ -6368,19 +6368,19 @@
     </row>
     <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C187">
         <v>1128</v>
       </c>
       <c r="D187" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E187" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F187" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G187" t="s">
         <v>10</v>
@@ -6400,19 +6400,19 @@
     </row>
     <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C188">
         <v>914</v>
       </c>
       <c r="D188" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E188" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F188" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G188" t="s">
         <v>10</v>
@@ -6432,19 +6432,19 @@
     </row>
     <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C189">
         <v>1130</v>
       </c>
       <c r="D189" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E189" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F189" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G189" t="s">
         <v>10</v>
@@ -6464,19 +6464,19 @@
     </row>
     <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C190">
         <v>1129</v>
       </c>
       <c r="D190" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E190" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F190" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G190" t="s">
         <v>10</v>
@@ -6496,19 +6496,19 @@
     </row>
     <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C191">
         <v>771</v>
       </c>
       <c r="D191" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E191" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F191" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G191" t="s">
         <v>10</v>
@@ -6528,19 +6528,19 @@
     </row>
     <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C192">
         <v>2268</v>
       </c>
       <c r="D192" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E192" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F192" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G192" t="s">
         <v>10</v>
@@ -6560,19 +6560,19 @@
     </row>
     <row r="193" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C193">
         <v>1132</v>
       </c>
       <c r="D193" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E193" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F193" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G193" t="s">
         <v>10</v>
@@ -6592,19 +6592,19 @@
     </row>
     <row r="194" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C194">
         <v>2067</v>
       </c>
       <c r="D194" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E194" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F194" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G194" t="s">
         <v>10</v>
@@ -6624,19 +6624,19 @@
     </row>
     <row r="195" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C195">
         <v>1125</v>
       </c>
       <c r="D195" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E195" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F195" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G195" t="s">
         <v>10</v>
@@ -6656,19 +6656,19 @@
     </row>
     <row r="196" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C196">
         <v>1126</v>
       </c>
       <c r="D196" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E196" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F196" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G196" t="s">
         <v>10</v>
@@ -6688,19 +6688,19 @@
     </row>
     <row r="197" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C197">
         <v>1128</v>
       </c>
       <c r="D197" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E197" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F197" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G197" t="s">
         <v>10</v>
@@ -6720,19 +6720,19 @@
     </row>
     <row r="198" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C198">
         <v>914</v>
       </c>
       <c r="D198" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E198" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F198" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G198" t="s">
         <v>10</v>
@@ -6752,19 +6752,19 @@
     </row>
     <row r="199" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C199">
         <v>1130</v>
       </c>
       <c r="D199" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E199" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F199" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G199" t="s">
         <v>10</v>
@@ -6784,19 +6784,19 @@
     </row>
     <row r="200" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C200">
         <v>1129</v>
       </c>
       <c r="D200" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E200" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F200" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G200" t="s">
         <v>10</v>
@@ -6816,19 +6816,19 @@
     </row>
     <row r="201" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C201">
         <v>771</v>
       </c>
       <c r="D201" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E201" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F201" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G201" t="s">
         <v>10</v>
@@ -6848,19 +6848,19 @@
     </row>
     <row r="202" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C202">
         <v>2268</v>
       </c>
       <c r="D202" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E202" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F202" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G202" t="s">
         <v>10</v>
@@ -6880,19 +6880,19 @@
     </row>
     <row r="203" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C203">
         <v>1132</v>
       </c>
       <c r="D203" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E203" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F203" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G203" t="s">
         <v>10</v>
@@ -6912,19 +6912,19 @@
     </row>
     <row r="204" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C204">
         <v>2067</v>
       </c>
       <c r="D204" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E204" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F204" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G204" t="s">
         <v>10</v>
@@ -6944,19 +6944,19 @@
     </row>
     <row r="205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C205">
         <v>1125</v>
       </c>
       <c r="D205" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E205" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F205" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G205" t="s">
         <v>10</v>
@@ -6976,19 +6976,19 @@
     </row>
     <row r="206" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C206">
         <v>1126</v>
       </c>
       <c r="D206" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E206" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F206" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G206" t="s">
         <v>10</v>
@@ -7008,19 +7008,19 @@
     </row>
     <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C207">
         <v>1128</v>
       </c>
       <c r="D207" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E207" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F207" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G207" t="s">
         <v>10</v>
@@ -7040,19 +7040,19 @@
     </row>
     <row r="208" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C208">
         <v>914</v>
       </c>
       <c r="D208" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E208" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F208" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G208" t="s">
         <v>10</v>
@@ -7072,19 +7072,19 @@
     </row>
     <row r="209" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C209">
         <v>1130</v>
       </c>
       <c r="D209" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E209" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F209" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G209" t="s">
         <v>10</v>
@@ -7104,19 +7104,19 @@
     </row>
     <row r="210" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C210">
         <v>1129</v>
       </c>
       <c r="D210" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E210" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F210" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G210" t="s">
         <v>12</v>
@@ -7138,24 +7138,24 @@
       <c r="H211" s="2"/>
       <c r="I211" s="1"/>
       <c r="K211" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="212" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C212">
         <v>771</v>
       </c>
       <c r="D212" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F212" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G212" t="s">
         <v>10</v>
@@ -7175,19 +7175,19 @@
     </row>
     <row r="213" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C213">
         <v>2268</v>
       </c>
       <c r="D213" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E213" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F213" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G213" t="s">
         <v>10</v>
@@ -7207,7 +7207,7 @@
     </row>
     <row r="214" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C214">
         <v>4661</v>
@@ -7216,10 +7216,10 @@
         <v>54</v>
       </c>
       <c r="E214" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F214" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G214" t="s">
         <v>10</v>
@@ -7239,19 +7239,19 @@
     </row>
     <row r="215" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C215">
         <v>1132</v>
       </c>
       <c r="D215" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E215" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F215" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G215" t="s">
         <v>10</v>
@@ -7271,19 +7271,19 @@
     </row>
     <row r="216" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C216">
         <v>2067</v>
       </c>
       <c r="D216" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E216" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F216" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G216" t="s">
         <v>10</v>
@@ -7303,19 +7303,19 @@
     </row>
     <row r="217" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C217">
         <v>1125</v>
       </c>
       <c r="D217" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E217" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F217" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G217" t="s">
         <v>10</v>
@@ -7335,19 +7335,19 @@
     </row>
     <row r="218" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C218">
         <v>1126</v>
       </c>
       <c r="D218" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E218" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F218" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G218" t="s">
         <v>10</v>
@@ -7367,19 +7367,19 @@
     </row>
     <row r="219" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C219">
         <v>1128</v>
       </c>
       <c r="D219" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E219" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F219" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G219" t="s">
         <v>10</v>
@@ -7399,19 +7399,19 @@
     </row>
     <row r="220" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C220">
         <v>914</v>
       </c>
       <c r="D220" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E220" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F220" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G220" t="s">
         <v>10</v>
@@ -7431,19 +7431,19 @@
     </row>
     <row r="221" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C221">
         <v>1130</v>
       </c>
       <c r="D221" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E221" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F221" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G221" t="s">
         <v>10</v>
@@ -7463,19 +7463,19 @@
     </row>
     <row r="222" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C222">
         <v>1129</v>
       </c>
       <c r="D222" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E222" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F222" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G222" t="s">
         <v>10</v>
@@ -7495,19 +7495,19 @@
     </row>
     <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C223">
         <v>771</v>
       </c>
       <c r="D223" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E223" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F223" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G223" t="s">
         <v>10</v>
@@ -7527,19 +7527,19 @@
     </row>
     <row r="224" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C224">
         <v>2268</v>
       </c>
       <c r="D224" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E224" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F224" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G224" t="s">
         <v>10</v>
@@ -7559,7 +7559,7 @@
     </row>
     <row r="225" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C225">
         <v>4661</v>
@@ -7568,10 +7568,10 @@
         <v>54</v>
       </c>
       <c r="E225" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F225" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G225" t="s">
         <v>10</v>
@@ -7591,19 +7591,19 @@
     </row>
     <row r="226" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C226">
         <v>1132</v>
       </c>
       <c r="D226" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E226" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F226" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G226" t="s">
         <v>10</v>
@@ -7623,19 +7623,19 @@
     </row>
     <row r="227" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C227">
         <v>2067</v>
       </c>
       <c r="D227" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E227" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F227" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G227" t="s">
         <v>10</v>
@@ -7655,19 +7655,19 @@
     </row>
     <row r="228" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C228">
         <v>1125</v>
       </c>
       <c r="D228" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E228" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F228" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G228" t="s">
         <v>10</v>
@@ -7687,19 +7687,19 @@
     </row>
     <row r="229" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C229">
         <v>1126</v>
       </c>
       <c r="D229" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E229" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F229" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G229" t="s">
         <v>10</v>
@@ -7719,19 +7719,19 @@
     </row>
     <row r="230" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C230">
         <v>1128</v>
       </c>
       <c r="D230" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E230" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F230" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G230" t="s">
         <v>10</v>
@@ -7751,19 +7751,19 @@
     </row>
     <row r="231" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C231">
         <v>914</v>
       </c>
       <c r="D231" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E231" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F231" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G231" t="s">
         <v>10</v>
@@ -7783,19 +7783,19 @@
     </row>
     <row r="232" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C232">
         <v>1130</v>
       </c>
       <c r="D232" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E232" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F232" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G232" t="s">
         <v>10</v>
@@ -7815,19 +7815,19 @@
     </row>
     <row r="233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C233">
         <v>1129</v>
       </c>
       <c r="D233" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E233" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F233" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G233" t="s">
         <v>10</v>
@@ -7847,19 +7847,19 @@
     </row>
     <row r="234" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C234">
         <v>771</v>
       </c>
       <c r="D234" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E234" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F234" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G234" t="s">
         <v>10</v>
@@ -7879,19 +7879,19 @@
     </row>
     <row r="235" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C235">
         <v>2268</v>
       </c>
       <c r="D235" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E235" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F235" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G235" t="s">
         <v>10</v>
@@ -7911,7 +7911,7 @@
     </row>
     <row r="236" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C236">
         <v>4661</v>
@@ -7920,10 +7920,10 @@
         <v>54</v>
       </c>
       <c r="E236" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F236" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G236" t="s">
         <v>10</v>
@@ -7943,19 +7943,19 @@
     </row>
     <row r="237" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C237">
         <v>1132</v>
       </c>
       <c r="D237" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E237" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F237" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G237" t="s">
         <v>10</v>
@@ -7975,19 +7975,19 @@
     </row>
     <row r="238" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C238">
         <v>2067</v>
       </c>
       <c r="D238" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E238" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F238" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G238" t="s">
         <v>10</v>
@@ -8007,19 +8007,19 @@
     </row>
     <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C239">
         <v>1125</v>
       </c>
       <c r="D239" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E239" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F239" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G239" t="s">
         <v>10</v>
@@ -8039,19 +8039,19 @@
     </row>
     <row r="240" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C240">
         <v>1126</v>
       </c>
       <c r="D240" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E240" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F240" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G240" t="s">
         <v>10</v>
@@ -8071,19 +8071,19 @@
     </row>
     <row r="241" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C241">
         <v>1128</v>
       </c>
       <c r="D241" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E241" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F241" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G241" t="s">
         <v>10</v>
@@ -8103,19 +8103,19 @@
     </row>
     <row r="242" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C242">
         <v>914</v>
       </c>
       <c r="D242" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E242" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F242" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G242" t="s">
         <v>10</v>
@@ -8135,19 +8135,19 @@
     </row>
     <row r="243" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C243">
         <v>1130</v>
       </c>
       <c r="D243" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E243" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F243" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G243" t="s">
         <v>10</v>
@@ -8167,19 +8167,19 @@
     </row>
     <row r="244" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C244">
         <v>1129</v>
       </c>
       <c r="D244" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E244" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F244" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G244" t="s">
         <v>10</v>
@@ -8199,19 +8199,19 @@
     </row>
     <row r="245" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C245">
         <v>771</v>
       </c>
       <c r="D245" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F245" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G245" t="s">
         <v>10</v>
@@ -8231,19 +8231,19 @@
     </row>
     <row r="246" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C246">
         <v>2268</v>
       </c>
       <c r="D246" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E246" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F246" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G246" t="s">
         <v>10</v>
@@ -8263,7 +8263,7 @@
     </row>
     <row r="247" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C247">
         <v>4661</v>
@@ -8272,10 +8272,10 @@
         <v>54</v>
       </c>
       <c r="E247" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F247" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G247" t="s">
         <v>10</v>
@@ -8295,19 +8295,19 @@
     </row>
     <row r="248" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C248">
         <v>1132</v>
       </c>
       <c r="D248" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E248" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F248" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G248" t="s">
         <v>10</v>
@@ -8327,19 +8327,19 @@
     </row>
     <row r="249" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C249">
         <v>2067</v>
       </c>
       <c r="D249" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E249" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F249" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G249" t="s">
         <v>13</v>
@@ -8359,19 +8359,19 @@
     </row>
     <row r="250" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B250" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C250">
         <v>1125</v>
       </c>
       <c r="D250" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E250" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F250" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G250" t="s">
         <v>10</v>
@@ -8391,19 +8391,19 @@
     </row>
     <row r="251" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C251">
         <v>1126</v>
       </c>
       <c r="D251" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E251" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F251" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G251" t="s">
         <v>10</v>
@@ -8423,19 +8423,19 @@
     </row>
     <row r="252" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C252">
         <v>1128</v>
       </c>
       <c r="D252" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E252" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F252" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G252" t="s">
         <v>10</v>
@@ -8455,19 +8455,19 @@
     </row>
     <row r="253" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C253">
         <v>914</v>
       </c>
       <c r="D253" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E253" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F253" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G253" t="s">
         <v>10</v>
@@ -8487,19 +8487,19 @@
     </row>
     <row r="254" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C254">
         <v>1130</v>
       </c>
       <c r="D254" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E254" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F254" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G254" t="s">
         <v>10</v>
@@ -8519,19 +8519,19 @@
     </row>
     <row r="255" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B255" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C255">
         <v>1129</v>
       </c>
       <c r="D255" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E255" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F255" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G255" t="s">
         <v>10</v>
@@ -8551,19 +8551,19 @@
     </row>
     <row r="256" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B256" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C256">
         <v>771</v>
       </c>
       <c r="D256" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F256" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G256" t="s">
         <v>10</v>
@@ -8583,19 +8583,19 @@
     </row>
     <row r="257" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B257" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C257">
         <v>2268</v>
       </c>
       <c r="D257" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E257" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F257" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G257" t="s">
         <v>10</v>
@@ -8615,7 +8615,7 @@
     </row>
     <row r="258" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C258">
         <v>4661</v>
@@ -8624,10 +8624,10 @@
         <v>54</v>
       </c>
       <c r="E258" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F258" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G258" t="s">
         <v>10</v>
@@ -8647,19 +8647,19 @@
     </row>
     <row r="259" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B259" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C259">
         <v>1132</v>
       </c>
       <c r="D259" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E259" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F259" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G259" t="s">
         <v>13</v>
@@ -8679,19 +8679,19 @@
     </row>
     <row r="260" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C260">
         <v>2067</v>
       </c>
       <c r="D260" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E260" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F260" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G260" t="s">
         <v>10</v>
@@ -8711,19 +8711,19 @@
     </row>
     <row r="261" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B261" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C261">
         <v>1125</v>
       </c>
       <c r="D261" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E261" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F261" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G261" t="s">
         <v>10</v>
@@ -8743,19 +8743,19 @@
     </row>
     <row r="262" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B262" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C262">
         <v>1126</v>
       </c>
       <c r="D262" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E262" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F262" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G262" t="s">
         <v>10</v>
@@ -8775,19 +8775,19 @@
     </row>
     <row r="263" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B263" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C263">
         <v>1128</v>
       </c>
       <c r="D263" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E263" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F263" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G263" t="s">
         <v>10</v>
@@ -8807,19 +8807,19 @@
     </row>
     <row r="264" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B264" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C264">
         <v>914</v>
       </c>
       <c r="D264" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E264" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F264" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G264" t="s">
         <v>10</v>
@@ -8839,19 +8839,19 @@
     </row>
     <row r="265" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B265" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C265">
         <v>1130</v>
       </c>
       <c r="D265" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E265" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F265" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G265" t="s">
         <v>10</v>
@@ -8871,19 +8871,19 @@
     </row>
     <row r="266" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C266">
         <v>1129</v>
       </c>
       <c r="D266" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E266" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F266" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G266" t="s">
         <v>10</v>
@@ -8903,19 +8903,19 @@
     </row>
     <row r="267" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C267">
         <v>771</v>
       </c>
       <c r="D267" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F267" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G267" t="s">
         <v>10</v>
@@ -8935,19 +8935,19 @@
     </row>
     <row r="268" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C268">
         <v>2268</v>
       </c>
       <c r="D268" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E268" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F268" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G268" t="s">
         <v>10</v>
@@ -8967,7 +8967,7 @@
     </row>
     <row r="269" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B269" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C269">
         <v>4661</v>
@@ -8976,10 +8976,10 @@
         <v>54</v>
       </c>
       <c r="E269" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F269" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G269" t="s">
         <v>10</v>
@@ -8999,19 +8999,19 @@
     </row>
     <row r="270" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B270" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C270">
         <v>1132</v>
       </c>
       <c r="D270" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E270" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F270" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G270" t="s">
         <v>10</v>
@@ -9031,19 +9031,19 @@
     </row>
     <row r="271" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B271" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C271">
         <v>2067</v>
       </c>
       <c r="D271" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E271" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F271" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G271" t="s">
         <v>10</v>
@@ -9063,19 +9063,19 @@
     </row>
     <row r="272" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C272">
         <v>1125</v>
       </c>
       <c r="D272" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E272" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F272" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G272" t="s">
         <v>10</v>
@@ -9095,19 +9095,19 @@
     </row>
     <row r="273" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C273">
         <v>1126</v>
       </c>
       <c r="D273" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E273" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F273" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G273" t="s">
         <v>10</v>
@@ -9127,19 +9127,19 @@
     </row>
     <row r="274" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B274" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C274">
         <v>1128</v>
       </c>
       <c r="D274" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E274" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F274" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G274" t="s">
         <v>10</v>
@@ -9159,19 +9159,19 @@
     </row>
     <row r="275" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B275" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C275">
         <v>914</v>
       </c>
       <c r="D275" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E275" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F275" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G275" t="s">
         <v>10</v>
@@ -9191,19 +9191,19 @@
     </row>
     <row r="276" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B276" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C276">
         <v>1130</v>
       </c>
       <c r="D276" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E276" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F276" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G276" t="s">
         <v>10</v>
@@ -9223,19 +9223,19 @@
     </row>
     <row r="277" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C277">
         <v>1129</v>
       </c>
       <c r="D277" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E277" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F277" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G277" t="s">
         <v>10</v>
@@ -9255,19 +9255,19 @@
     </row>
     <row r="278" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B278" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C278">
         <v>771</v>
       </c>
       <c r="D278" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F278" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G278" t="s">
         <v>10</v>
@@ -9287,19 +9287,19 @@
     </row>
     <row r="279" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C279">
         <v>2268</v>
       </c>
       <c r="D279" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E279" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F279" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G279" t="s">
         <v>10</v>
@@ -9319,7 +9319,7 @@
     </row>
     <row r="280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B280" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C280">
         <v>4661</v>
@@ -9328,10 +9328,10 @@
         <v>54</v>
       </c>
       <c r="E280" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F280" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G280" t="s">
         <v>10</v>
@@ -9351,19 +9351,19 @@
     </row>
     <row r="281" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B281" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C281">
         <v>1132</v>
       </c>
       <c r="D281" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E281" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F281" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G281" t="s">
         <v>10</v>
@@ -9383,19 +9383,19 @@
     </row>
     <row r="282" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B282" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C282">
         <v>2067</v>
       </c>
       <c r="D282" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E282" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F282" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G282" t="s">
         <v>13</v>
@@ -9407,7 +9407,7 @@
         <v>46118.757986111108</v>
       </c>
       <c r="J282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K282" t="s">
         <v>11</v>
@@ -9415,19 +9415,19 @@
     </row>
     <row r="283" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B283" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C283">
         <v>1125</v>
       </c>
       <c r="D283" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E283" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F283" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G283" t="s">
         <v>12</v>
@@ -9449,24 +9449,24 @@
       <c r="H284" s="2"/>
       <c r="I284" s="1"/>
       <c r="K284" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="285" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C285">
         <v>1126</v>
       </c>
       <c r="D285" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E285" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F285" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G285" t="s">
         <v>10</v>
@@ -9486,19 +9486,19 @@
     </row>
     <row r="286" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C286">
         <v>1128</v>
       </c>
       <c r="D286" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E286" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F286" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G286" t="s">
         <v>12</v>
@@ -9520,24 +9520,24 @@
       <c r="H287" s="2"/>
       <c r="I287" s="1"/>
       <c r="K287" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="288" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C288">
         <v>914</v>
       </c>
       <c r="D288" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E288" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F288" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G288" t="s">
         <v>10</v>
@@ -9557,31 +9557,31 @@
     </row>
     <row r="289" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C289">
         <v>1130</v>
       </c>
       <c r="D289" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E289" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F289" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G289" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H289" s="2">
-        <v>0</v>
+        <v>6.2962962962962964E-3</v>
       </c>
       <c r="I289" s="1">
         <v>46118.760069444441</v>
       </c>
       <c r="J289">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K289" t="s">
         <v>11</v>
@@ -9589,19 +9589,19 @@
     </row>
     <row r="290" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C290">
         <v>1129</v>
       </c>
       <c r="D290" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E290" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F290" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G290" t="s">
         <v>10</v>
@@ -9621,19 +9621,19 @@
     </row>
     <row r="291" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C291">
         <v>771</v>
       </c>
       <c r="D291" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F291" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G291" t="s">
         <v>10</v>
@@ -9653,19 +9653,19 @@
     </row>
     <row r="292" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C292">
         <v>2268</v>
       </c>
       <c r="D292" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E292" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F292" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G292" t="s">
         <v>12</v>
@@ -9687,12 +9687,12 @@
       <c r="H293" s="2"/>
       <c r="I293" s="1"/>
       <c r="K293" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="294" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C294">
         <v>4661</v>
@@ -9701,10 +9701,10 @@
         <v>54</v>
       </c>
       <c r="E294" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F294" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G294" t="s">
         <v>10</v>
@@ -9724,19 +9724,19 @@
     </row>
     <row r="295" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C295">
         <v>1132</v>
       </c>
       <c r="D295" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E295" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F295" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G295" t="s">
         <v>12</v>
@@ -9758,7 +9758,7 @@
       <c r="H296" s="2"/>
       <c r="I296" s="1"/>
       <c r="K296" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="297" spans="2:11" x14ac:dyDescent="0.25">

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCC428B-3A45-4C51-AC6D-BCE3527D64B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83557BE1-D6B3-42A8-9056-E6CFB53510BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="56">
   <si>
     <t>Company Name</t>
   </si>
@@ -9407,7 +9407,7 @@
         <v>46118.757986111108</v>
       </c>
       <c r="J282">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K282" t="s">
         <v>11</v>
@@ -9762,98 +9762,406 @@
       </c>
     </row>
     <row r="297" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H297" s="2"/>
-      <c r="I297" s="1"/>
+      <c r="B297" t="s">
+        <v>23</v>
+      </c>
+      <c r="C297">
+        <v>2067</v>
+      </c>
+      <c r="D297" t="s">
+        <v>39</v>
+      </c>
+      <c r="E297" t="s">
+        <v>25</v>
+      </c>
+      <c r="F297" t="s">
+        <v>44</v>
+      </c>
+      <c r="G297" t="s">
+        <v>13</v>
+      </c>
+      <c r="H297" s="2">
+        <v>0</v>
+      </c>
+      <c r="I297" s="1">
+        <v>46146.632523148146</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="298" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H298" s="2"/>
-      <c r="I298" s="1"/>
+      <c r="B298" t="s">
+        <v>23</v>
+      </c>
+      <c r="C298">
+        <v>1125</v>
+      </c>
+      <c r="D298" t="s">
+        <v>27</v>
+      </c>
+      <c r="E298" t="s">
+        <v>25</v>
+      </c>
+      <c r="F298" t="s">
+        <v>44</v>
+      </c>
+      <c r="G298" t="s">
+        <v>13</v>
+      </c>
+      <c r="H298" s="2">
+        <v>0</v>
+      </c>
+      <c r="I298" s="1">
+        <v>46146.632523148146</v>
+      </c>
+      <c r="J298">
+        <v>0</v>
+      </c>
+      <c r="K298" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="299" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H299" s="2"/>
-      <c r="I299" s="1"/>
+      <c r="B299" t="s">
+        <v>23</v>
+      </c>
+      <c r="C299">
+        <v>1126</v>
+      </c>
+      <c r="D299" t="s">
+        <v>29</v>
+      </c>
+      <c r="E299" t="s">
+        <v>25</v>
+      </c>
+      <c r="F299" t="s">
+        <v>44</v>
+      </c>
+      <c r="G299" t="s">
+        <v>10</v>
+      </c>
+      <c r="H299" s="2">
+        <v>4.4212962962962964E-3</v>
+      </c>
+      <c r="I299" s="1">
+        <v>46146.633217592593</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="300" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H300" s="2"/>
-      <c r="I300" s="1"/>
+      <c r="B300" t="s">
+        <v>23</v>
+      </c>
+      <c r="C300">
+        <v>1128</v>
+      </c>
+      <c r="D300" t="s">
+        <v>30</v>
+      </c>
+      <c r="E300" t="s">
+        <v>25</v>
+      </c>
+      <c r="F300" t="s">
+        <v>44</v>
+      </c>
+      <c r="G300" t="s">
+        <v>13</v>
+      </c>
+      <c r="H300" s="2">
+        <v>0</v>
+      </c>
+      <c r="I300" s="1">
+        <v>46146.633217592593</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="301" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H301" s="2"/>
-      <c r="I301" s="1"/>
+      <c r="B301" t="s">
+        <v>23</v>
+      </c>
+      <c r="C301">
+        <v>914</v>
+      </c>
+      <c r="D301" t="s">
+        <v>31</v>
+      </c>
+      <c r="E301" t="s">
+        <v>25</v>
+      </c>
+      <c r="F301" t="s">
+        <v>44</v>
+      </c>
+      <c r="G301" t="s">
+        <v>13</v>
+      </c>
+      <c r="H301" s="2">
+        <v>0</v>
+      </c>
+      <c r="I301" s="1">
+        <v>46146.633912037039</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="302" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H302" s="2"/>
-      <c r="I302" s="1"/>
+      <c r="B302" t="s">
+        <v>23</v>
+      </c>
+      <c r="C302">
+        <v>1130</v>
+      </c>
+      <c r="D302" t="s">
+        <v>32</v>
+      </c>
+      <c r="E302" t="s">
+        <v>25</v>
+      </c>
+      <c r="F302" t="s">
+        <v>44</v>
+      </c>
+      <c r="G302" t="s">
+        <v>13</v>
+      </c>
+      <c r="H302" s="2">
+        <v>0</v>
+      </c>
+      <c r="I302" s="1">
+        <v>46146.634606481479</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="303" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H303" s="2"/>
-      <c r="I303" s="1"/>
+      <c r="B303" t="s">
+        <v>23</v>
+      </c>
+      <c r="C303">
+        <v>1129</v>
+      </c>
+      <c r="D303" t="s">
+        <v>33</v>
+      </c>
+      <c r="E303" t="s">
+        <v>25</v>
+      </c>
+      <c r="F303" t="s">
+        <v>44</v>
+      </c>
+      <c r="G303" t="s">
+        <v>13</v>
+      </c>
+      <c r="H303" s="2">
+        <v>0</v>
+      </c>
+      <c r="I303" s="1">
+        <v>46146.634606481479</v>
+      </c>
+      <c r="J303">
+        <v>0</v>
+      </c>
+      <c r="K303" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="304" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H304" s="2"/>
-      <c r="I304" s="1"/>
-    </row>
-    <row r="305" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H305" s="2"/>
-      <c r="I305" s="1"/>
-    </row>
-    <row r="306" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H306" s="2"/>
-      <c r="I306" s="1"/>
-    </row>
-    <row r="307" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H307" s="2"/>
-      <c r="I307" s="1"/>
-    </row>
-    <row r="308" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B304" t="s">
+        <v>23</v>
+      </c>
+      <c r="C304">
+        <v>771</v>
+      </c>
+      <c r="D304" t="s">
+        <v>34</v>
+      </c>
+      <c r="E304" t="s">
+        <v>25</v>
+      </c>
+      <c r="F304" t="s">
+        <v>44</v>
+      </c>
+      <c r="G304" t="s">
+        <v>13</v>
+      </c>
+      <c r="H304" s="2">
+        <v>0</v>
+      </c>
+      <c r="I304" s="1">
+        <v>46146.635300925926</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="305" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B305" t="s">
+        <v>23</v>
+      </c>
+      <c r="C305">
+        <v>2268</v>
+      </c>
+      <c r="D305" t="s">
+        <v>25</v>
+      </c>
+      <c r="E305" t="s">
+        <v>25</v>
+      </c>
+      <c r="F305" t="s">
+        <v>44</v>
+      </c>
+      <c r="G305" t="s">
+        <v>13</v>
+      </c>
+      <c r="H305" s="2">
+        <v>0</v>
+      </c>
+      <c r="I305" s="1">
+        <v>46146.635995370372</v>
+      </c>
+      <c r="J305">
+        <v>0</v>
+      </c>
+      <c r="K305" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="306" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B306" t="s">
+        <v>23</v>
+      </c>
+      <c r="C306">
+        <v>4661</v>
+      </c>
+      <c r="D306" t="s">
+        <v>54</v>
+      </c>
+      <c r="E306" t="s">
+        <v>25</v>
+      </c>
+      <c r="F306" t="s">
+        <v>44</v>
+      </c>
+      <c r="G306" t="s">
+        <v>13</v>
+      </c>
+      <c r="H306" s="2">
+        <v>0</v>
+      </c>
+      <c r="I306" s="1">
+        <v>46146.635995370372</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="307" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B307" t="s">
+        <v>23</v>
+      </c>
+      <c r="C307">
+        <v>1132</v>
+      </c>
+      <c r="D307" t="s">
+        <v>35</v>
+      </c>
+      <c r="E307" t="s">
+        <v>25</v>
+      </c>
+      <c r="F307" t="s">
+        <v>44</v>
+      </c>
+      <c r="G307" t="s">
+        <v>13</v>
+      </c>
+      <c r="H307" s="2">
+        <v>0</v>
+      </c>
+      <c r="I307" s="1">
+        <v>46146.636689814812</v>
+      </c>
+      <c r="J307">
+        <v>0</v>
+      </c>
+      <c r="K307" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="308" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H308" s="2"/>
       <c r="I308" s="1"/>
     </row>
-    <row r="309" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H309" s="2"/>
       <c r="I309" s="1"/>
     </row>
-    <row r="310" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H310" s="2"/>
       <c r="I310" s="1"/>
     </row>
-    <row r="311" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H311" s="2"/>
       <c r="I311" s="1"/>
     </row>
-    <row r="312" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H312" s="2"/>
       <c r="I312" s="1"/>
     </row>
-    <row r="313" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H313" s="2"/>
       <c r="I313" s="1"/>
     </row>
-    <row r="314" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H314" s="2"/>
       <c r="I314" s="1"/>
     </row>
-    <row r="315" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H315" s="2"/>
       <c r="I315" s="1"/>
     </row>
-    <row r="316" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H316" s="2"/>
       <c r="I316" s="1"/>
     </row>
-    <row r="317" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H317" s="2"/>
       <c r="I317" s="1"/>
     </row>
-    <row r="318" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H318" s="2"/>
       <c r="I318" s="1"/>
     </row>
-    <row r="319" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H319" s="2"/>
       <c r="I319" s="1"/>
     </row>
-    <row r="320" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H320" s="2"/>
       <c r="I320" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83557BE1-D6B3-42A8-9056-E6CFB53510BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07B3CD0-4C06-43BF-94D0-E6BF3A00428F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -9407,7 +9407,7 @@
         <v>46118.757986111108</v>
       </c>
       <c r="J282">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K282" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EF7A40-2534-40D9-BF96-D59B49AAF2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2242A1B5-04A2-4CCC-926E-D49ED537300A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -9787,7 +9787,7 @@
         <v>46146.632523148146</v>
       </c>
       <c r="J297">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K297" t="s">
         <v>11</v>
@@ -9819,7 +9819,7 @@
         <v>46146.632523148146</v>
       </c>
       <c r="J298">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K298" t="s">
         <v>11</v>
@@ -9883,7 +9883,7 @@
         <v>46146.633217592593</v>
       </c>
       <c r="J300">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K300" t="s">
         <v>11</v>
@@ -9947,7 +9947,7 @@
         <v>46146.634606481479</v>
       </c>
       <c r="J302">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K302" t="s">
         <v>11</v>
@@ -9979,7 +9979,7 @@
         <v>46146.634606481479</v>
       </c>
       <c r="J303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K303" t="s">
         <v>11</v>
@@ -10075,7 +10075,7 @@
         <v>46146.635995370372</v>
       </c>
       <c r="J306">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K306" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Curtis Garage- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Curtis-Garage-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A3BF523-1179-419D-A425-AC17E11440B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8E5529-D8DC-436A-8FBC-0CCD58CA5474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -10197,7 +10197,7 @@
         <v>46176.470370370371</v>
       </c>
       <c r="J309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K309" t="s">
         <v>11</v>
@@ -10293,7 +10293,7 @@
         <v>46176.471064814818</v>
       </c>
       <c r="J312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K312" t="s">
         <v>11</v>
@@ -10316,16 +10316,16 @@
         <v>25</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H313" s="2">
-        <v>0</v>
+        <v>9.6296296296296303E-3</v>
       </c>
       <c r="I313" s="1">
         <v>46176.471759259257</v>
       </c>
       <c r="J313">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K313" t="s">
         <v>11</v>
@@ -10389,7 +10389,7 @@
         <v>46176.472453703704</v>
       </c>
       <c r="J315">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K315" t="s">
         <v>11</v>
@@ -10444,16 +10444,16 @@
         <v>25</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H317" s="2">
-        <v>0</v>
+        <v>1.0185185185185186E-2</v>
       </c>
       <c r="I317" s="1">
         <v>46176.47314814815</v>
       </c>
       <c r="J317">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K317" t="s">
         <v>11</v>
@@ -10485,7 +10485,7 @@
         <v>46176.47314814815</v>
       </c>
       <c r="J318">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K318" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Curtis-Garage-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F485D0D-2236-44B7-8E2B-391BC25C92C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8EC24D2-5680-4C06-A5E8-CFA7A8CD52F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -89,6 +89,9 @@
     <t>Speed Management</t>
   </si>
   <si>
+    <t>Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -101,13 +104,22 @@
     <t>Space Management-Big 5</t>
   </si>
   <si>
+    <t>Distracted Driving</t>
+  </si>
+  <si>
     <t>Alert Driving</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -119,6 +131,45 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
+    <t>DNU-Driver Health</t>
+  </si>
+  <si>
+    <t>DNU-Scene of an Accident</t>
+  </si>
+  <si>
+    <t>DNU-NEW-Vehicle Inspections</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
+  </si>
+  <si>
+    <t>Micro-Learn Speed</t>
+  </si>
+  <si>
+    <t>Micro-Learn Space Mangement</t>
+  </si>
+  <si>
+    <t>Dangers of Aggressive Driving for CMV Drivers</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
+  </si>
+  <si>
+    <t>3 points of contact</t>
+  </si>
+  <si>
+    <t>Vehicle &amp; Roadside Inspections CMV</t>
+  </si>
+  <si>
+    <t>Safe RR Crossing</t>
+  </si>
+  <si>
+    <t>In Cab Distractions</t>
+  </si>
+  <si>
+    <t>DNU-Fatigue</t>
+  </si>
+  <si>
     <t>Curtis Garage and Wrecker</t>
   </si>
   <si>
@@ -126,9 +177,6 @@
   </si>
   <si>
     <t>Tammy Thompson</t>
-  </si>
-  <si>
-    <t>DNU-Driver Health</t>
   </si>
   <si>
     <t>Douglas Phillippo</t>
@@ -158,58 +206,10 @@
     <t>Wesley Bell</t>
   </si>
   <si>
-    <t>DNU-Fatigue</t>
-  </si>
-  <si>
-    <t>DNU-Scene of an Accident</t>
-  </si>
-  <si>
-    <t>DNU-NEW-Vehicle Inspections</t>
-  </si>
-  <si>
     <t>Cole Curtis</t>
   </si>
   <si>
-    <t>Vehicle Inspections</t>
-  </si>
-  <si>
-    <t>Distracted Driving</t>
-  </si>
-  <si>
-    <t>Safe RR Crossing</t>
-  </si>
-  <si>
-    <t>3 points of contact</t>
-  </si>
-  <si>
-    <t>In Cab Distractions</t>
-  </si>
-  <si>
-    <t>Micro-Learn Speed</t>
-  </si>
-  <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>Micro-Learn Space Mangement</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Fire Extinguisher Training for CDL</t>
-  </si>
-  <si>
     <t>Walker Sims</t>
-  </si>
-  <si>
-    <t>Vehicle &amp; Roadside Inspections CMV</t>
-  </si>
-  <si>
-    <t>Camera Event Management Orientation for Drivers</t>
   </si>
 </sst>
 </file>
@@ -583,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -632,19 +632,19 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E2">
         <v>1124</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -664,19 +664,19 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E3">
         <v>1125</v>
       </c>
       <c r="F3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -696,16 +696,16 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E4">
         <v>1127</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -725,19 +725,19 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E5">
         <v>1126</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -757,19 +757,19 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E6">
         <v>1128</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -789,19 +789,19 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E7">
         <v>914</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -821,19 +821,19 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <v>1130</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -853,19 +853,19 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E9">
         <v>1129</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -885,19 +885,19 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E10">
         <v>771</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -917,16 +917,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E11">
         <v>1626</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -946,19 +946,19 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <v>1132</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -978,19 +978,19 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E13">
         <v>1124</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -1010,19 +1010,19 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E14">
         <v>1125</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -1042,19 +1042,19 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E15">
         <v>1126</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1074,19 +1074,19 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E16">
         <v>1128</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1106,19 +1106,19 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E17">
         <v>914</v>
       </c>
       <c r="F17" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G17" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>13</v>
@@ -1138,19 +1138,19 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E18">
         <v>1130</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G18" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1170,19 +1170,19 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E19">
         <v>1129</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G19" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>12</v>
@@ -1206,24 +1206,24 @@
       <c r="J20" s="2"/>
       <c r="K20" s="1"/>
       <c r="M20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E21">
         <v>771</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1243,19 +1243,19 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E22">
         <v>1132</v>
       </c>
       <c r="F22" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -1275,19 +1275,19 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E23">
         <v>1124</v>
       </c>
       <c r="F23" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G23" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1307,19 +1307,19 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E24">
         <v>1125</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G24" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1339,19 +1339,19 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E25">
         <v>1126</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G25" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1371,19 +1371,19 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E26">
         <v>1128</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G26" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1403,19 +1403,19 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E27">
         <v>914</v>
       </c>
       <c r="F27" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G27" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1435,19 +1435,19 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E28">
         <v>1130</v>
       </c>
       <c r="F28" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1467,19 +1467,19 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E29">
         <v>1129</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G29" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>12</v>
@@ -1503,24 +1503,24 @@
       <c r="J30" s="2"/>
       <c r="K30" s="1"/>
       <c r="M30" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E31">
         <v>771</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G31" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1540,19 +1540,19 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E32">
         <v>1132</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G32" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1572,19 +1572,19 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E33">
         <v>1124</v>
       </c>
       <c r="F33" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G33" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>13</v>
@@ -1604,19 +1604,19 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E34">
         <v>2067</v>
       </c>
       <c r="F34" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G34" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -1636,19 +1636,19 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E35">
         <v>1125</v>
       </c>
       <c r="F35" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G35" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1668,19 +1668,19 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E36">
         <v>1126</v>
       </c>
       <c r="F36" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="G36" t="s">
-        <v>28</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1700,19 +1700,19 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E37">
         <v>1128</v>
       </c>
       <c r="F37" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G37" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
@@ -1732,19 +1732,19 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E38">
         <v>914</v>
       </c>
       <c r="F38" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G38" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1764,19 +1764,19 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E39">
         <v>1130</v>
       </c>
       <c r="F39" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G39" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>12</v>
@@ -1800,24 +1800,24 @@
       <c r="J40" s="2"/>
       <c r="K40" s="1"/>
       <c r="M40" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E41">
         <v>1129</v>
       </c>
       <c r="F41" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G41" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>13</v>
@@ -1837,19 +1837,19 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E42">
         <v>771</v>
       </c>
       <c r="F42" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G42" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1869,19 +1869,19 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E43">
         <v>1132</v>
       </c>
       <c r="F43" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G43" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>12</v>
@@ -1905,24 +1905,24 @@
       <c r="J44" s="2"/>
       <c r="K44" s="1"/>
       <c r="M44" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E45">
         <v>1124</v>
       </c>
       <c r="F45" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G45" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1942,19 +1942,19 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E46">
         <v>2067</v>
       </c>
       <c r="F46" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G46" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
@@ -1974,19 +1974,19 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E47">
         <v>1125</v>
       </c>
       <c r="F47" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G47" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -2006,19 +2006,19 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E48">
         <v>1130</v>
       </c>
       <c r="F48" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G48" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -2038,19 +2038,19 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E49">
         <v>1129</v>
       </c>
       <c r="F49" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G49" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -2070,19 +2070,19 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E50">
         <v>1132</v>
       </c>
       <c r="F50" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G50" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -2102,19 +2102,19 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E51">
         <v>2268</v>
       </c>
       <c r="F51" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G51" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -2134,19 +2134,19 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E52">
         <v>1130</v>
       </c>
       <c r="F52" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G52" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>12</v>
@@ -2170,24 +2170,24 @@
       <c r="J53" s="2"/>
       <c r="K53" s="1"/>
       <c r="M53" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E54">
         <v>1130</v>
       </c>
       <c r="F54" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G54" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2207,16 +2207,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E55">
         <v>1130</v>
       </c>
       <c r="F55" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G55" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -2243,24 +2243,24 @@
       <c r="J56" s="2"/>
       <c r="K56" s="1"/>
       <c r="M56" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E57">
         <v>1124</v>
       </c>
       <c r="F57" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G57" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2280,19 +2280,19 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E58">
         <v>2067</v>
       </c>
       <c r="F58" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G58" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2312,19 +2312,19 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E59">
         <v>1125</v>
       </c>
       <c r="F59" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G59" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2344,19 +2344,19 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E60">
         <v>1126</v>
       </c>
       <c r="F60" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G60" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2376,19 +2376,19 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E61">
         <v>1128</v>
       </c>
       <c r="F61" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G61" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>10</v>
@@ -2408,19 +2408,19 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E62">
         <v>914</v>
       </c>
       <c r="F62" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G62" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2440,19 +2440,19 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E63">
         <v>1130</v>
       </c>
       <c r="F63" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G63" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E64">
         <v>1129</v>
       </c>
       <c r="F64" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G64" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2504,19 +2504,19 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E65">
         <v>771</v>
       </c>
       <c r="F65" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G65" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2536,19 +2536,19 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E66">
         <v>2268</v>
       </c>
       <c r="F66" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G66" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2568,19 +2568,19 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E67">
         <v>1132</v>
       </c>
       <c r="F67" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G67" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2600,19 +2600,19 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E68">
         <v>771</v>
       </c>
       <c r="F68" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G68" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2632,19 +2632,19 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E69">
         <v>771</v>
       </c>
       <c r="F69" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G69" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2664,16 +2664,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E70">
         <v>771</v>
       </c>
       <c r="F70" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G70" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -2696,16 +2696,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E71">
         <v>1128</v>
       </c>
       <c r="F71" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G71" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -2728,19 +2728,19 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E72">
         <v>1128</v>
       </c>
       <c r="F72" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G72" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>10</v>
@@ -2760,19 +2760,19 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E73">
         <v>1128</v>
       </c>
       <c r="F73" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G73" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2792,19 +2792,19 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E74">
         <v>1124</v>
       </c>
       <c r="F74" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G74" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2824,19 +2824,19 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E75">
         <v>2067</v>
       </c>
       <c r="F75" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G75" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>12</v>
@@ -2860,24 +2860,24 @@
       <c r="J76" s="2"/>
       <c r="K76" s="1"/>
       <c r="M76" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E77">
         <v>1125</v>
       </c>
       <c r="F77" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G77" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2897,19 +2897,19 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E78">
         <v>1126</v>
       </c>
       <c r="F78" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G78" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>10</v>
@@ -2929,19 +2929,19 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E79">
         <v>1128</v>
       </c>
       <c r="F79" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G79" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>10</v>
@@ -2961,19 +2961,19 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E80">
         <v>914</v>
       </c>
       <c r="F80" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G80" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2993,19 +2993,19 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E81">
         <v>1130</v>
       </c>
       <c r="F81" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G81" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -3025,19 +3025,19 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E82">
         <v>1129</v>
       </c>
       <c r="F82" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G82" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -3057,19 +3057,19 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E83">
         <v>771</v>
       </c>
       <c r="F83" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G83" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -3089,19 +3089,19 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E84">
         <v>2268</v>
       </c>
       <c r="F84" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G84" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -3121,19 +3121,19 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E85">
         <v>1132</v>
       </c>
       <c r="F85" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G85" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -3153,19 +3153,19 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E86">
         <v>1124</v>
       </c>
       <c r="F86" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G86" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -3185,19 +3185,19 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E87">
         <v>1125</v>
       </c>
       <c r="F87" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G87" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -3217,19 +3217,19 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E88">
         <v>1129</v>
       </c>
       <c r="F88" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G88" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3249,19 +3249,19 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E89">
         <v>1124</v>
       </c>
       <c r="F89" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G89" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -3281,19 +3281,19 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E90">
         <v>1125</v>
       </c>
       <c r="F90" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G90" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3313,19 +3313,19 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E91">
         <v>1129</v>
       </c>
       <c r="F91" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G91" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -3345,19 +3345,19 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E92">
         <v>1124</v>
       </c>
       <c r="F92" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G92" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3377,19 +3377,19 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E93">
         <v>1125</v>
       </c>
       <c r="F93" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G93" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3409,19 +3409,19 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E94">
         <v>1129</v>
       </c>
       <c r="F94" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G94" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>13</v>
@@ -3441,16 +3441,16 @@
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E95">
         <v>1124</v>
       </c>
       <c r="F95" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G95" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -3473,16 +3473,16 @@
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E96">
         <v>1125</v>
       </c>
       <c r="F96" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G96" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -3505,16 +3505,16 @@
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E97">
         <v>1129</v>
       </c>
       <c r="F97" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G97" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
@@ -3537,19 +3537,19 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E98">
         <v>1124</v>
       </c>
       <c r="F98" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G98" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3569,19 +3569,19 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E99">
         <v>2067</v>
       </c>
       <c r="F99" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G99" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3601,19 +3601,19 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E100">
         <v>1125</v>
       </c>
       <c r="F100" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G100" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3633,19 +3633,19 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E101">
         <v>1126</v>
       </c>
       <c r="F101" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G101" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -3665,19 +3665,19 @@
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E102">
         <v>1128</v>
       </c>
       <c r="F102" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G102" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>10</v>
@@ -3697,19 +3697,19 @@
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E103">
         <v>914</v>
       </c>
       <c r="F103" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G103" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>10</v>
@@ -3729,19 +3729,19 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E104">
         <v>1130</v>
       </c>
       <c r="F104" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G104" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3761,19 +3761,19 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E105">
         <v>1129</v>
       </c>
       <c r="F105" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G105" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3793,19 +3793,19 @@
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E106">
         <v>771</v>
       </c>
       <c r="F106" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G106" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3825,19 +3825,19 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E107">
         <v>2268</v>
       </c>
       <c r="F107" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G107" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3857,19 +3857,19 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E108">
         <v>1132</v>
       </c>
       <c r="F108" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G108" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3889,19 +3889,19 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E109">
         <v>1124</v>
       </c>
       <c r="F109" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G109" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>10</v>
@@ -3921,19 +3921,19 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E110">
         <v>2067</v>
       </c>
       <c r="F110" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G110" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3953,19 +3953,19 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E111">
         <v>1125</v>
       </c>
       <c r="F111" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G111" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3985,19 +3985,19 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E112">
         <v>1126</v>
       </c>
       <c r="F112" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G112" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -4017,19 +4017,19 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E113">
         <v>1128</v>
       </c>
       <c r="F113" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G113" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>10</v>
@@ -4049,19 +4049,19 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E114">
         <v>914</v>
       </c>
       <c r="F114" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G114" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>10</v>
@@ -4081,19 +4081,19 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E115">
         <v>1130</v>
       </c>
       <c r="F115" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G115" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -4113,19 +4113,19 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E116">
         <v>1129</v>
       </c>
       <c r="F116" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G116" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -4145,19 +4145,19 @@
     </row>
     <row r="117" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E117">
         <v>771</v>
       </c>
       <c r="F117" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G117" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>10</v>
@@ -4177,19 +4177,19 @@
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E118">
         <v>2268</v>
       </c>
       <c r="F118" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G118" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -4209,19 +4209,19 @@
     </row>
     <row r="119" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E119">
         <v>1132</v>
       </c>
       <c r="F119" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G119" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -4241,19 +4241,19 @@
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E120">
         <v>1124</v>
       </c>
       <c r="F120" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G120" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>10</v>
@@ -4273,19 +4273,19 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E121">
         <v>2067</v>
       </c>
       <c r="F121" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G121" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -4305,19 +4305,19 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E122">
         <v>1125</v>
       </c>
       <c r="F122" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G122" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -4337,19 +4337,19 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E123">
         <v>1126</v>
       </c>
       <c r="F123" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G123" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>10</v>
@@ -4369,19 +4369,19 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E124">
         <v>1128</v>
       </c>
       <c r="F124" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G124" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -4401,19 +4401,19 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E125">
         <v>914</v>
       </c>
       <c r="F125" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G125" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -4433,19 +4433,19 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E126">
         <v>1130</v>
       </c>
       <c r="F126" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G126" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -4465,19 +4465,19 @@
     </row>
     <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E127">
         <v>1129</v>
       </c>
       <c r="F127" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G127" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>10</v>
@@ -4497,19 +4497,19 @@
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E128">
         <v>771</v>
       </c>
       <c r="F128" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G128" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>10</v>
@@ -4529,19 +4529,19 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E129">
         <v>2268</v>
       </c>
       <c r="F129" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G129" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>10</v>
@@ -4561,19 +4561,19 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E130">
         <v>1132</v>
       </c>
       <c r="F130" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G130" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>10</v>
@@ -4593,19 +4593,19 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E131">
         <v>1124</v>
       </c>
       <c r="F131" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G131" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>10</v>
@@ -4625,19 +4625,19 @@
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E132">
         <v>2067</v>
       </c>
       <c r="F132" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G132" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>10</v>
@@ -4657,19 +4657,19 @@
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E133">
         <v>1125</v>
       </c>
       <c r="F133" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G133" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>10</v>
@@ -4689,19 +4689,19 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E134">
         <v>1126</v>
       </c>
       <c r="F134" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G134" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4721,19 +4721,19 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E135">
         <v>1128</v>
       </c>
       <c r="F135" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G135" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4753,19 +4753,19 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E136">
         <v>914</v>
       </c>
       <c r="F136" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G136" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4785,19 +4785,19 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E137">
         <v>1130</v>
       </c>
       <c r="F137" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G137" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>10</v>
@@ -4817,19 +4817,19 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E138">
         <v>1129</v>
       </c>
       <c r="F138" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G138" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>10</v>
@@ -4849,19 +4849,19 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E139">
         <v>771</v>
       </c>
       <c r="F139" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G139" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>10</v>
@@ -4881,19 +4881,19 @@
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E140">
         <v>2268</v>
       </c>
       <c r="F140" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G140" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>10</v>
@@ -4913,19 +4913,19 @@
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E141">
         <v>1132</v>
       </c>
       <c r="F141" t="s">
+        <v>54</v>
+      </c>
+      <c r="G141" t="s">
+        <v>45</v>
+      </c>
+      <c r="H141" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="G141" t="s">
-        <v>28</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>10</v>
@@ -4945,19 +4945,19 @@
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D142" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E142">
         <v>1124</v>
       </c>
       <c r="F142" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G142" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>10</v>
@@ -4977,19 +4977,19 @@
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E143">
         <v>2067</v>
       </c>
       <c r="F143" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G143" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -5009,19 +5009,19 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E144">
         <v>1125</v>
       </c>
       <c r="F144" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G144" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>10</v>
@@ -5041,19 +5041,19 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E145">
         <v>1126</v>
       </c>
       <c r="F145" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G145" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -5073,19 +5073,19 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E146">
         <v>1128</v>
       </c>
       <c r="F146" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G146" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -5105,19 +5105,19 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E147">
         <v>914</v>
       </c>
       <c r="F147" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G147" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>10</v>
@@ -5137,19 +5137,19 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E148">
         <v>1130</v>
       </c>
       <c r="F148" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G148" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>10</v>
@@ -5169,19 +5169,19 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E149">
         <v>1129</v>
       </c>
       <c r="F149" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G149" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>10</v>
@@ -5201,19 +5201,19 @@
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E150">
         <v>771</v>
       </c>
       <c r="F150" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G150" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>10</v>
@@ -5233,19 +5233,19 @@
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E151">
         <v>2268</v>
       </c>
       <c r="F151" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G151" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>10</v>
@@ -5265,19 +5265,19 @@
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E152">
         <v>1132</v>
       </c>
       <c r="F152" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G152" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>10</v>
@@ -5297,19 +5297,19 @@
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E153">
         <v>1124</v>
       </c>
       <c r="F153" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G153" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>10</v>
@@ -5329,19 +5329,19 @@
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E154">
         <v>2067</v>
       </c>
       <c r="F154" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G154" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>10</v>
@@ -5361,19 +5361,19 @@
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E155">
         <v>1125</v>
       </c>
       <c r="F155" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G155" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>10</v>
@@ -5393,19 +5393,19 @@
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E156">
         <v>1126</v>
       </c>
       <c r="F156" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G156" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>10</v>
@@ -5425,19 +5425,19 @@
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E157">
         <v>1128</v>
       </c>
       <c r="F157" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G157" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>10</v>
@@ -5457,19 +5457,19 @@
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E158">
         <v>914</v>
       </c>
       <c r="F158" t="s">
+        <v>50</v>
+      </c>
+      <c r="G158" t="s">
+        <v>45</v>
+      </c>
+      <c r="H158" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="G158" t="s">
-        <v>28</v>
-      </c>
-      <c r="H158" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>10</v>
@@ -5489,19 +5489,19 @@
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E159">
         <v>1130</v>
       </c>
       <c r="F159" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G159" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>10</v>
@@ -5521,19 +5521,19 @@
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E160">
         <v>1129</v>
       </c>
       <c r="F160" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G160" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>10</v>
@@ -5553,19 +5553,19 @@
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E161">
         <v>771</v>
       </c>
       <c r="F161" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G161" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>10</v>
@@ -5585,19 +5585,19 @@
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E162">
         <v>2268</v>
       </c>
       <c r="F162" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G162" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>10</v>
@@ -5617,19 +5617,19 @@
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E163">
         <v>1132</v>
       </c>
       <c r="F163" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G163" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>10</v>
@@ -5649,19 +5649,19 @@
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E164">
         <v>2067</v>
       </c>
       <c r="F164" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G164" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>10</v>
@@ -5681,19 +5681,19 @@
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D165" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E165">
         <v>1125</v>
       </c>
       <c r="F165" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G165" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>10</v>
@@ -5713,19 +5713,19 @@
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D166" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E166">
         <v>1126</v>
       </c>
       <c r="F166" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G166" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>10</v>
@@ -5745,19 +5745,19 @@
     </row>
     <row r="167" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D167" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E167">
         <v>1128</v>
       </c>
       <c r="F167" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G167" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>10</v>
@@ -5777,19 +5777,19 @@
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E168">
         <v>914</v>
       </c>
       <c r="F168" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G168" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>10</v>
@@ -5809,19 +5809,19 @@
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D169" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E169">
         <v>1130</v>
       </c>
       <c r="F169" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G169" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>10</v>
@@ -5841,19 +5841,19 @@
     </row>
     <row r="170" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D170" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E170">
         <v>1129</v>
       </c>
       <c r="F170" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G170" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>10</v>
@@ -5873,19 +5873,19 @@
     </row>
     <row r="171" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D171" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E171">
         <v>771</v>
       </c>
       <c r="F171" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G171" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>10</v>
@@ -5905,19 +5905,19 @@
     </row>
     <row r="172" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D172" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E172">
         <v>2268</v>
       </c>
       <c r="F172" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G172" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5937,19 +5937,19 @@
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D173" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E173">
         <v>1132</v>
       </c>
       <c r="F173" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G173" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>10</v>
@@ -5969,19 +5969,19 @@
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D174" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E174">
         <v>2067</v>
       </c>
       <c r="F174" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G174" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>13</v>
@@ -6001,19 +6001,19 @@
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D175" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E175">
         <v>1125</v>
       </c>
       <c r="F175" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G175" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -6033,19 +6033,19 @@
     </row>
     <row r="176" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D176" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E176">
         <v>1126</v>
       </c>
       <c r="F176" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G176" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>10</v>
@@ -6065,19 +6065,19 @@
     </row>
     <row r="177" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D177" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E177">
         <v>1128</v>
       </c>
       <c r="F177" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G177" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>10</v>
@@ -6097,19 +6097,19 @@
     </row>
     <row r="178" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D178" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E178">
         <v>914</v>
       </c>
       <c r="F178" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G178" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -6129,19 +6129,19 @@
     </row>
     <row r="179" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D179" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E179">
         <v>1130</v>
       </c>
       <c r="F179" t="s">
+        <v>51</v>
+      </c>
+      <c r="G179" t="s">
+        <v>45</v>
+      </c>
+      <c r="H179" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="G179" t="s">
-        <v>28</v>
-      </c>
-      <c r="H179" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>13</v>
@@ -6161,19 +6161,19 @@
     </row>
     <row r="180" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D180" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E180">
         <v>1129</v>
       </c>
       <c r="F180" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G180" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>10</v>
@@ -6193,19 +6193,19 @@
     </row>
     <row r="181" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D181" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E181">
         <v>771</v>
       </c>
       <c r="F181" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G181" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>10</v>
@@ -6225,19 +6225,19 @@
     </row>
     <row r="182" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D182" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E182">
         <v>2268</v>
       </c>
       <c r="F182" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G182" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>10</v>
@@ -6257,19 +6257,19 @@
     </row>
     <row r="183" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E183">
         <v>1132</v>
       </c>
       <c r="F183" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G183" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>10</v>
@@ -6289,19 +6289,19 @@
     </row>
     <row r="184" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D184" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E184">
         <v>2067</v>
       </c>
       <c r="F184" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G184" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>10</v>
@@ -6321,19 +6321,19 @@
     </row>
     <row r="185" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D185" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E185">
         <v>1125</v>
       </c>
       <c r="F185" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G185" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>10</v>
@@ -6353,19 +6353,19 @@
     </row>
     <row r="186" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D186" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E186">
         <v>1126</v>
       </c>
       <c r="F186" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G186" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>10</v>
@@ -6385,19 +6385,19 @@
     </row>
     <row r="187" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D187" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E187">
         <v>1128</v>
       </c>
       <c r="F187" t="s">
+        <v>49</v>
+      </c>
+      <c r="G187" t="s">
+        <v>45</v>
+      </c>
+      <c r="H187" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="G187" t="s">
-        <v>28</v>
-      </c>
-      <c r="H187" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>10</v>
@@ -6417,19 +6417,19 @@
     </row>
     <row r="188" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D188" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E188">
         <v>914</v>
       </c>
       <c r="F188" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G188" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>10</v>
@@ -6449,19 +6449,19 @@
     </row>
     <row r="189" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D189" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E189">
         <v>1130</v>
       </c>
       <c r="F189" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G189" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -6481,19 +6481,19 @@
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D190" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E190">
         <v>1129</v>
       </c>
       <c r="F190" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G190" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>10</v>
@@ -6513,19 +6513,19 @@
     </row>
     <row r="191" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D191" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E191">
         <v>771</v>
       </c>
       <c r="F191" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G191" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>10</v>
@@ -6545,19 +6545,19 @@
     </row>
     <row r="192" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D192" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E192">
         <v>2268</v>
       </c>
       <c r="F192" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G192" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>10</v>
@@ -6577,19 +6577,19 @@
     </row>
     <row r="193" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D193" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E193">
         <v>1132</v>
       </c>
       <c r="F193" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G193" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>10</v>
@@ -6609,19 +6609,19 @@
     </row>
     <row r="194" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D194" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E194">
         <v>2067</v>
       </c>
       <c r="F194" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G194" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -6641,19 +6641,19 @@
     </row>
     <row r="195" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D195" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E195">
         <v>1125</v>
       </c>
       <c r="F195" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G195" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -6673,19 +6673,19 @@
     </row>
     <row r="196" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D196" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E196">
         <v>1126</v>
       </c>
       <c r="F196" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G196" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>10</v>
@@ -6705,19 +6705,19 @@
     </row>
     <row r="197" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D197" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E197">
         <v>1128</v>
       </c>
       <c r="F197" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G197" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>10</v>
@@ -6737,19 +6737,19 @@
     </row>
     <row r="198" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D198" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E198">
         <v>914</v>
       </c>
       <c r="F198" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G198" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>10</v>
@@ -6769,19 +6769,19 @@
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D199" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E199">
         <v>1130</v>
       </c>
       <c r="F199" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G199" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>10</v>
@@ -6801,19 +6801,19 @@
     </row>
     <row r="200" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D200" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E200">
         <v>1129</v>
       </c>
       <c r="F200" t="s">
+        <v>52</v>
+      </c>
+      <c r="G200" t="s">
+        <v>45</v>
+      </c>
+      <c r="H200" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="G200" t="s">
-        <v>28</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>10</v>
@@ -6833,19 +6833,19 @@
     </row>
     <row r="201" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D201" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E201">
         <v>771</v>
       </c>
       <c r="F201" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G201" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>10</v>
@@ -6865,19 +6865,19 @@
     </row>
     <row r="202" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D202" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E202">
         <v>2268</v>
       </c>
       <c r="F202" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G202" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>10</v>
@@ -6897,19 +6897,19 @@
     </row>
     <row r="203" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D203" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E203">
         <v>1132</v>
       </c>
       <c r="F203" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G203" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>10</v>
@@ -6929,19 +6929,19 @@
     </row>
     <row r="204" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D204" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E204">
         <v>2067</v>
       </c>
       <c r="F204" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G204" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>10</v>
@@ -6961,19 +6961,19 @@
     </row>
     <row r="205" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D205" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E205">
         <v>1125</v>
       </c>
       <c r="F205" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G205" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>10</v>
@@ -6993,19 +6993,19 @@
     </row>
     <row r="206" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D206" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E206">
         <v>1126</v>
       </c>
       <c r="F206" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G206" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>10</v>
@@ -7025,19 +7025,19 @@
     </row>
     <row r="207" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D207" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E207">
         <v>1128</v>
       </c>
       <c r="F207" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G207" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>10</v>
@@ -7057,19 +7057,19 @@
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D208" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E208">
         <v>914</v>
       </c>
       <c r="F208" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G208" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>10</v>
@@ -7089,19 +7089,19 @@
     </row>
     <row r="209" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D209" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E209">
         <v>1130</v>
       </c>
       <c r="F209" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G209" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>10</v>
@@ -7121,19 +7121,19 @@
     </row>
     <row r="210" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D210" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E210">
         <v>1129</v>
       </c>
       <c r="F210" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G210" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>12</v>
@@ -7157,24 +7157,24 @@
       <c r="J211" s="2"/>
       <c r="K211" s="1"/>
       <c r="M211" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="212" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D212" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E212">
         <v>771</v>
       </c>
       <c r="F212" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G212" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -7194,19 +7194,19 @@
     </row>
     <row r="213" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D213" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E213">
         <v>2268</v>
       </c>
       <c r="F213" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G213" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>10</v>
@@ -7226,19 +7226,19 @@
     </row>
     <row r="214" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D214" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E214">
         <v>4661</v>
       </c>
       <c r="F214" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G214" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -7258,19 +7258,19 @@
     </row>
     <row r="215" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D215" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E215">
         <v>1132</v>
       </c>
       <c r="F215" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G215" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -7290,19 +7290,19 @@
     </row>
     <row r="216" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D216" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E216">
         <v>2067</v>
       </c>
       <c r="F216" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G216" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -7322,19 +7322,19 @@
     </row>
     <row r="217" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D217" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E217">
         <v>1125</v>
       </c>
       <c r="F217" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G217" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -7354,19 +7354,19 @@
     </row>
     <row r="218" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D218" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E218">
         <v>1126</v>
       </c>
       <c r="F218" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G218" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>10</v>
@@ -7386,19 +7386,19 @@
     </row>
     <row r="219" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D219" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E219">
         <v>1128</v>
       </c>
       <c r="F219" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G219" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>10</v>
@@ -7418,19 +7418,19 @@
     </row>
     <row r="220" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D220" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E220">
         <v>914</v>
       </c>
       <c r="F220" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G220" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>10</v>
@@ -7450,19 +7450,19 @@
     </row>
     <row r="221" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D221" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E221">
         <v>1130</v>
       </c>
       <c r="F221" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G221" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>10</v>
@@ -7482,19 +7482,19 @@
     </row>
     <row r="222" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D222" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E222">
         <v>1129</v>
       </c>
       <c r="F222" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G222" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>10</v>
@@ -7514,19 +7514,19 @@
     </row>
     <row r="223" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D223" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E223">
         <v>771</v>
       </c>
       <c r="F223" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G223" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>10</v>
@@ -7546,19 +7546,19 @@
     </row>
     <row r="224" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D224" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E224">
         <v>2268</v>
       </c>
       <c r="F224" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G224" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>10</v>
@@ -7578,19 +7578,19 @@
     </row>
     <row r="225" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D225" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E225">
         <v>4661</v>
       </c>
       <c r="F225" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G225" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>10</v>
@@ -7610,19 +7610,19 @@
     </row>
     <row r="226" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D226" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E226">
         <v>1132</v>
       </c>
       <c r="F226" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G226" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>10</v>
@@ -7642,19 +7642,19 @@
     </row>
     <row r="227" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D227" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E227">
         <v>2067</v>
       </c>
       <c r="F227" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G227" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>10</v>
@@ -7674,19 +7674,19 @@
     </row>
     <row r="228" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D228" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E228">
         <v>1125</v>
       </c>
       <c r="F228" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G228" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>10</v>
@@ -7706,19 +7706,19 @@
     </row>
     <row r="229" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D229" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E229">
         <v>1126</v>
       </c>
       <c r="F229" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G229" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -7738,19 +7738,19 @@
     </row>
     <row r="230" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D230" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E230">
         <v>1128</v>
       </c>
       <c r="F230" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G230" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -7770,19 +7770,19 @@
     </row>
     <row r="231" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D231" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E231">
         <v>914</v>
       </c>
       <c r="F231" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G231" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>10</v>
@@ -7802,19 +7802,19 @@
     </row>
     <row r="232" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D232" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E232">
         <v>1130</v>
       </c>
       <c r="F232" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G232" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>10</v>
@@ -7834,19 +7834,19 @@
     </row>
     <row r="233" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D233" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E233">
         <v>1129</v>
       </c>
       <c r="F233" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G233" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>10</v>
@@ -7866,19 +7866,19 @@
     </row>
     <row r="234" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D234" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E234">
         <v>771</v>
       </c>
       <c r="F234" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G234" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>10</v>
@@ -7898,19 +7898,19 @@
     </row>
     <row r="235" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D235" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E235">
         <v>2268</v>
       </c>
       <c r="F235" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G235" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>10</v>
@@ -7930,19 +7930,19 @@
     </row>
     <row r="236" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D236" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E236">
         <v>4661</v>
       </c>
       <c r="F236" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G236" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>10</v>
@@ -7962,19 +7962,19 @@
     </row>
     <row r="237" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D237" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E237">
         <v>1132</v>
       </c>
       <c r="F237" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G237" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -7994,19 +7994,19 @@
     </row>
     <row r="238" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D238" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E238">
         <v>2067</v>
       </c>
       <c r="F238" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G238" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -8026,19 +8026,19 @@
     </row>
     <row r="239" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D239" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E239">
         <v>1125</v>
       </c>
       <c r="F239" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G239" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>10</v>
@@ -8058,19 +8058,19 @@
     </row>
     <row r="240" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D240" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E240">
         <v>1126</v>
       </c>
       <c r="F240" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G240" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>10</v>
@@ -8090,19 +8090,19 @@
     </row>
     <row r="241" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D241" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E241">
         <v>1128</v>
       </c>
       <c r="F241" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G241" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>10</v>
@@ -8122,19 +8122,19 @@
     </row>
     <row r="242" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D242" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E242">
         <v>914</v>
       </c>
       <c r="F242" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G242" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>10</v>
@@ -8154,19 +8154,19 @@
     </row>
     <row r="243" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D243" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E243">
         <v>1130</v>
       </c>
       <c r="F243" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G243" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>10</v>
@@ -8186,19 +8186,19 @@
     </row>
     <row r="244" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D244" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E244">
         <v>1129</v>
       </c>
       <c r="F244" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G244" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>10</v>
@@ -8218,19 +8218,19 @@
     </row>
     <row r="245" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D245" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E245">
         <v>771</v>
       </c>
       <c r="F245" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G245" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>10</v>
@@ -8250,19 +8250,19 @@
     </row>
     <row r="246" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D246" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E246">
         <v>2268</v>
       </c>
       <c r="F246" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G246" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>10</v>
@@ -8282,19 +8282,19 @@
     </row>
     <row r="247" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D247" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E247">
         <v>4661</v>
       </c>
       <c r="F247" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G247" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -8314,19 +8314,19 @@
     </row>
     <row r="248" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D248" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E248">
         <v>1132</v>
       </c>
       <c r="F248" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G248" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -8346,19 +8346,19 @@
     </row>
     <row r="249" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D249" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E249">
         <v>2067</v>
       </c>
       <c r="F249" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G249" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>13</v>
@@ -8378,19 +8378,19 @@
     </row>
     <row r="250" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D250" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E250">
         <v>1125</v>
       </c>
       <c r="F250" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G250" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>10</v>
@@ -8410,19 +8410,19 @@
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D251" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E251">
         <v>1126</v>
       </c>
       <c r="F251" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G251" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>10</v>
@@ -8442,19 +8442,19 @@
     </row>
     <row r="252" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D252" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E252">
         <v>1128</v>
       </c>
       <c r="F252" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G252" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>10</v>
@@ -8474,19 +8474,19 @@
     </row>
     <row r="253" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D253" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E253">
         <v>914</v>
       </c>
       <c r="F253" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G253" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>10</v>
@@ -8506,19 +8506,19 @@
     </row>
     <row r="254" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D254" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E254">
         <v>1130</v>
       </c>
       <c r="F254" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G254" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -8538,19 +8538,19 @@
     </row>
     <row r="255" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D255" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E255">
         <v>1129</v>
       </c>
       <c r="F255" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G255" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -8570,19 +8570,19 @@
     </row>
     <row r="256" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D256" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E256">
         <v>771</v>
       </c>
       <c r="F256" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G256" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>10</v>
@@ -8602,19 +8602,19 @@
     </row>
     <row r="257" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D257" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E257">
         <v>2268</v>
       </c>
       <c r="F257" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G257" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -8634,19 +8634,19 @@
     </row>
     <row r="258" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D258" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E258">
         <v>4661</v>
       </c>
       <c r="F258" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G258" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>10</v>
@@ -8666,19 +8666,19 @@
     </row>
     <row r="259" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D259" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E259">
         <v>1132</v>
       </c>
       <c r="F259" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G259" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -8698,19 +8698,19 @@
     </row>
     <row r="260" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D260" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E260">
         <v>2067</v>
       </c>
       <c r="F260" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G260" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>10</v>
@@ -8730,19 +8730,19 @@
     </row>
     <row r="261" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D261" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E261">
         <v>1125</v>
       </c>
       <c r="F261" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G261" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -8762,19 +8762,19 @@
     </row>
     <row r="262" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D262" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E262">
         <v>1126</v>
       </c>
       <c r="F262" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G262" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>10</v>
@@ -8794,19 +8794,19 @@
     </row>
     <row r="263" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D263" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E263">
         <v>1128</v>
       </c>
       <c r="F263" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G263" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>10</v>
@@ -8826,19 +8826,19 @@
     </row>
     <row r="264" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D264" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E264">
         <v>914</v>
       </c>
       <c r="F264" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G264" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -8858,19 +8858,19 @@
     </row>
     <row r="265" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D265" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E265">
         <v>1130</v>
       </c>
       <c r="F265" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G265" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>10</v>
@@ -8890,19 +8890,19 @@
     </row>
     <row r="266" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D266" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E266">
         <v>1129</v>
       </c>
       <c r="F266" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G266" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -8922,19 +8922,19 @@
     </row>
     <row r="267" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D267" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E267">
         <v>771</v>
       </c>
       <c r="F267" t="s">
+        <v>53</v>
+      </c>
+      <c r="G267" t="s">
+        <v>45</v>
+      </c>
+      <c r="H267" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="G267" t="s">
-        <v>28</v>
-      </c>
-      <c r="H267" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>10</v>
@@ -8954,19 +8954,19 @@
     </row>
     <row r="268" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D268" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E268">
         <v>2268</v>
       </c>
       <c r="F268" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G268" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>10</v>
@@ -8986,19 +8986,19 @@
     </row>
     <row r="269" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D269" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E269">
         <v>4661</v>
       </c>
       <c r="F269" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G269" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>10</v>
@@ -9018,19 +9018,19 @@
     </row>
     <row r="270" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D270" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E270">
         <v>1132</v>
       </c>
       <c r="F270" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G270" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>10</v>
@@ -9050,19 +9050,19 @@
     </row>
     <row r="271" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D271" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E271">
         <v>2067</v>
       </c>
       <c r="F271" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G271" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>10</v>
@@ -9082,19 +9082,19 @@
     </row>
     <row r="272" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D272" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E272">
         <v>1125</v>
       </c>
       <c r="F272" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G272" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>10</v>
@@ -9114,19 +9114,19 @@
     </row>
     <row r="273" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D273" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E273">
         <v>1126</v>
       </c>
       <c r="F273" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G273" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>10</v>
@@ -9146,19 +9146,19 @@
     </row>
     <row r="274" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D274" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E274">
         <v>1128</v>
       </c>
       <c r="F274" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G274" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>10</v>
@@ -9178,19 +9178,19 @@
     </row>
     <row r="275" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D275" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E275">
         <v>914</v>
       </c>
       <c r="F275" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G275" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>10</v>
@@ -9210,19 +9210,19 @@
     </row>
     <row r="276" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D276" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E276">
         <v>1130</v>
       </c>
       <c r="F276" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G276" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>10</v>
@@ -9242,19 +9242,19 @@
     </row>
     <row r="277" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D277" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E277">
         <v>1129</v>
       </c>
       <c r="F277" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G277" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>10</v>
@@ -9274,19 +9274,19 @@
     </row>
     <row r="278" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D278" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E278">
         <v>771</v>
       </c>
       <c r="F278" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G278" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>10</v>
@@ -9306,19 +9306,19 @@
     </row>
     <row r="279" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D279" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E279">
         <v>2268</v>
       </c>
       <c r="F279" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G279" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>10</v>
@@ -9338,19 +9338,19 @@
     </row>
     <row r="280" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D280" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E280">
         <v>4661</v>
       </c>
       <c r="F280" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G280" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>10</v>
@@ -9370,19 +9370,19 @@
     </row>
     <row r="281" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D281" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E281">
         <v>1132</v>
       </c>
       <c r="F281" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G281" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -9402,19 +9402,19 @@
     </row>
     <row r="282" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D282" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E282">
         <v>2067</v>
       </c>
       <c r="F282" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G282" t="s">
+        <v>45</v>
+      </c>
+      <c r="H282" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="H282" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>13</v>
@@ -9434,19 +9434,19 @@
     </row>
     <row r="283" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D283" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E283">
         <v>1125</v>
       </c>
       <c r="F283" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G283" t="s">
+        <v>45</v>
+      </c>
+      <c r="H283" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="H283" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>12</v>
@@ -9470,24 +9470,24 @@
       <c r="J284" s="2"/>
       <c r="K284" s="1"/>
       <c r="M284" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="285" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D285" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E285">
         <v>1126</v>
       </c>
       <c r="F285" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G285" t="s">
+        <v>45</v>
+      </c>
+      <c r="H285" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="H285" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>10</v>
@@ -9507,19 +9507,19 @@
     </row>
     <row r="286" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D286" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E286">
         <v>1128</v>
       </c>
       <c r="F286" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G286" t="s">
+        <v>45</v>
+      </c>
+      <c r="H286" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="H286" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>12</v>
@@ -9543,24 +9543,24 @@
       <c r="J287" s="2"/>
       <c r="K287" s="1"/>
       <c r="M287" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="288" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D288" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E288">
         <v>914</v>
       </c>
       <c r="F288" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G288" t="s">
+        <v>45</v>
+      </c>
+      <c r="H288" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="H288" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>10</v>
@@ -9580,19 +9580,19 @@
     </row>
     <row r="289" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D289" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E289">
         <v>1130</v>
       </c>
       <c r="F289" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G289" t="s">
+        <v>45</v>
+      </c>
+      <c r="H289" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="H289" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>10</v>
@@ -9612,19 +9612,19 @@
     </row>
     <row r="290" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D290" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E290">
         <v>1129</v>
       </c>
       <c r="F290" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G290" t="s">
+        <v>45</v>
+      </c>
+      <c r="H290" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="H290" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>10</v>
@@ -9644,19 +9644,19 @@
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D291" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E291">
         <v>771</v>
       </c>
       <c r="F291" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G291" t="s">
+        <v>45</v>
+      </c>
+      <c r="H291" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="H291" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>10</v>
@@ -9676,19 +9676,19 @@
     </row>
     <row r="292" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D292" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E292">
         <v>2268</v>
       </c>
       <c r="F292" t="s">
+        <v>45</v>
+      </c>
+      <c r="G292" t="s">
+        <v>45</v>
+      </c>
+      <c r="H292" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G292" t="s">
-        <v>28</v>
-      </c>
-      <c r="H292" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>12</v>
@@ -9712,24 +9712,24 @@
       <c r="J293" s="2"/>
       <c r="K293" s="1"/>
       <c r="M293" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="294" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D294" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E294">
         <v>4661</v>
       </c>
       <c r="F294" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G294" t="s">
+        <v>45</v>
+      </c>
+      <c r="H294" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="H294" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -9749,19 +9749,19 @@
     </row>
     <row r="295" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D295" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E295">
         <v>1132</v>
       </c>
       <c r="F295" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G295" t="s">
+        <v>45</v>
+      </c>
+      <c r="H295" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="H295" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>12</v>
@@ -9785,24 +9785,24 @@
       <c r="J296" s="2"/>
       <c r="K296" s="1"/>
       <c r="M296" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="297" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D297" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E297">
         <v>2067</v>
       </c>
       <c r="F297" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G297" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>13</v>
@@ -9822,19 +9822,19 @@
     </row>
     <row r="298" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D298" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E298">
         <v>1125</v>
       </c>
       <c r="F298" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G298" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>10</v>
@@ -9854,19 +9854,19 @@
     </row>
     <row r="299" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D299" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E299">
         <v>1126</v>
       </c>
       <c r="F299" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G299" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>10</v>
@@ -9886,19 +9886,19 @@
     </row>
     <row r="300" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D300" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E300">
         <v>1128</v>
       </c>
       <c r="F300" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G300" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>10</v>
@@ -9918,19 +9918,19 @@
     </row>
     <row r="301" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D301" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E301">
         <v>914</v>
       </c>
       <c r="F301" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G301" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>10</v>
@@ -9950,19 +9950,19 @@
     </row>
     <row r="302" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D302" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E302">
         <v>1130</v>
       </c>
       <c r="F302" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G302" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>10</v>
@@ -9982,19 +9982,19 @@
     </row>
     <row r="303" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D303" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E303">
         <v>1129</v>
       </c>
       <c r="F303" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G303" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>10</v>
@@ -10014,19 +10014,19 @@
     </row>
     <row r="304" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D304" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E304">
         <v>771</v>
       </c>
       <c r="F304" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G304" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>10</v>
@@ -10046,19 +10046,19 @@
     </row>
     <row r="305" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D305" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E305">
         <v>2268</v>
       </c>
       <c r="F305" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G305" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>10</v>
@@ -10078,19 +10078,19 @@
     </row>
     <row r="306" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D306" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E306">
         <v>4661</v>
       </c>
       <c r="F306" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G306" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -10110,19 +10110,19 @@
     </row>
     <row r="307" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D307" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E307">
         <v>1132</v>
       </c>
       <c r="F307" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G307" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>10</v>
@@ -10142,19 +10142,19 @@
     </row>
     <row r="308" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D308" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E308">
         <v>1132</v>
       </c>
       <c r="F308" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G308" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>10</v>
@@ -10174,19 +10174,19 @@
     </row>
     <row r="309" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D309" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E309">
         <v>2067</v>
       </c>
       <c r="F309" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G309" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>13</v>
@@ -10206,19 +10206,19 @@
     </row>
     <row r="310" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D310" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E310">
         <v>1125</v>
       </c>
       <c r="F310" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G310" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>10</v>
@@ -10238,19 +10238,19 @@
     </row>
     <row r="311" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D311" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E311">
         <v>1126</v>
       </c>
       <c r="F311" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G311" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>10</v>
@@ -10270,19 +10270,19 @@
     </row>
     <row r="312" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D312" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E312">
         <v>1128</v>
       </c>
       <c r="F312" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G312" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>10</v>
@@ -10302,19 +10302,19 @@
     </row>
     <row r="313" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D313" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E313">
         <v>914</v>
       </c>
       <c r="F313" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G313" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>10</v>
@@ -10334,19 +10334,19 @@
     </row>
     <row r="314" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D314" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E314">
         <v>1130</v>
       </c>
       <c r="F314" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G314" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>10</v>
@@ -10366,19 +10366,19 @@
     </row>
     <row r="315" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D315" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E315">
         <v>1129</v>
       </c>
       <c r="F315" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G315" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>10</v>
@@ -10398,19 +10398,19 @@
     </row>
     <row r="316" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D316" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E316">
         <v>771</v>
       </c>
       <c r="F316" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G316" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>10</v>
@@ -10430,19 +10430,19 @@
     </row>
     <row r="317" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D317" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E317">
         <v>2268</v>
       </c>
       <c r="F317" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G317" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>10</v>
@@ -10462,19 +10462,19 @@
     </row>
     <row r="318" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D318" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E318">
         <v>4661</v>
       </c>
       <c r="F318" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G318" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>10</v>
@@ -10849,6 +10849,7 @@
     <row r="378" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H378" s="2"/>
       <c r="I378" s="1"/>
+      <c r="J378" s="2"/>
       <c r="K378" s="1"/>
     </row>
     <row r="379" spans="8:11" x14ac:dyDescent="0.3">
@@ -46915,7 +46916,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Curtis-Garage-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8EC24D2-5680-4C06-A5E8-CFA7A8CD52F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45674C86-352B-4EB2-B4C1-A7A5C7F037C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="57">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,10 +86,25 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
+  </si>
+  <si>
+    <t>DNU-Driver Health</t>
+  </si>
+  <si>
+    <t>DNU-Scene of an Accident</t>
+  </si>
+  <si>
+    <t>DNU-NEW-Vehicle Inspections</t>
   </si>
   <si>
     <t>Vehicle Inspections</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -101,28 +116,34 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Space Management-Big 5</t>
+    <t>Distracted Driving</t>
   </si>
   <si>
-    <t>Distracted Driving</t>
+    <t>Micro-Learn Speed</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
+  </si>
+  <si>
+    <t>Micro-Learn Space Mangement</t>
   </si>
   <si>
     <t>Alert Driving</t>
   </si>
   <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
+    <t>Space Management-Big 5</t>
+  </si>
+  <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
@@ -131,28 +152,7 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>DNU-Driver Health</t>
-  </si>
-  <si>
-    <t>DNU-Scene of an Accident</t>
-  </si>
-  <si>
-    <t>DNU-NEW-Vehicle Inspections</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Micro-Learn Speed</t>
-  </si>
-  <si>
-    <t>Micro-Learn Space Mangement</t>
-  </si>
-  <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>3 points of contact</t>
@@ -583,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -644,7 +644,7 @@
         <v>45</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -676,7 +676,7 @@
         <v>45</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -705,7 +705,7 @@
         <v>47</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -737,7 +737,7 @@
         <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -769,7 +769,7 @@
         <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -801,7 +801,7 @@
         <v>45</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -833,7 +833,7 @@
         <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -865,7 +865,7 @@
         <v>45</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -897,7 +897,7 @@
         <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -926,7 +926,7 @@
         <v>54</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -958,7 +958,7 @@
         <v>45</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -1206,7 +1206,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="1"/>
       <c r="M20" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
@@ -1287,7 +1287,7 @@
         <v>45</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1319,7 +1319,7 @@
         <v>45</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1351,7 +1351,7 @@
         <v>45</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1383,7 +1383,7 @@
         <v>45</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1415,7 +1415,7 @@
         <v>45</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1447,7 +1447,7 @@
         <v>45</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1479,7 +1479,7 @@
         <v>45</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>12</v>
@@ -1503,7 +1503,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="1"/>
       <c r="M30" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
@@ -1520,7 +1520,7 @@
         <v>45</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1552,7 +1552,7 @@
         <v>45</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1584,7 +1584,7 @@
         <v>45</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>13</v>
@@ -1616,7 +1616,7 @@
         <v>45</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -1648,7 +1648,7 @@
         <v>45</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1680,7 +1680,7 @@
         <v>45</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1712,7 +1712,7 @@
         <v>45</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
@@ -1744,7 +1744,7 @@
         <v>45</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1776,7 +1776,7 @@
         <v>45</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>12</v>
@@ -1800,7 +1800,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="1"/>
       <c r="M40" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
@@ -1817,7 +1817,7 @@
         <v>45</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>13</v>
@@ -1849,7 +1849,7 @@
         <v>45</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1881,7 +1881,7 @@
         <v>45</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>12</v>
@@ -1905,7 +1905,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="1"/>
       <c r="M44" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
@@ -1922,7 +1922,7 @@
         <v>45</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1954,7 +1954,7 @@
         <v>45</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
@@ -1986,7 +1986,7 @@
         <v>45</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -2018,7 +2018,7 @@
         <v>45</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -2050,7 +2050,7 @@
         <v>45</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -2082,7 +2082,7 @@
         <v>45</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -2114,7 +2114,7 @@
         <v>45</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -2146,7 +2146,7 @@
         <v>45</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>12</v>
@@ -2170,7 +2170,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="1"/>
       <c r="M53" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
@@ -2187,7 +2187,7 @@
         <v>45</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2219,7 +2219,7 @@
         <v>45</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>14</v>
@@ -2243,7 +2243,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="1"/>
       <c r="M56" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
@@ -2260,7 +2260,7 @@
         <v>45</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2292,7 +2292,7 @@
         <v>45</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2324,7 +2324,7 @@
         <v>45</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2356,7 +2356,7 @@
         <v>45</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2388,7 +2388,7 @@
         <v>45</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>10</v>
@@ -2420,7 +2420,7 @@
         <v>45</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2452,7 +2452,7 @@
         <v>45</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2484,7 +2484,7 @@
         <v>45</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2516,7 +2516,7 @@
         <v>45</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2548,7 +2548,7 @@
         <v>45</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2580,7 +2580,7 @@
         <v>45</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2612,7 +2612,7 @@
         <v>45</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2644,7 +2644,7 @@
         <v>45</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2676,7 +2676,7 @@
         <v>45</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2708,7 +2708,7 @@
         <v>45</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2740,7 +2740,7 @@
         <v>45</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>10</v>
@@ -2772,7 +2772,7 @@
         <v>45</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2804,7 +2804,7 @@
         <v>45</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2836,7 +2836,7 @@
         <v>45</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>12</v>
@@ -2860,7 +2860,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="1"/>
       <c r="M76" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
@@ -2877,7 +2877,7 @@
         <v>45</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2909,7 +2909,7 @@
         <v>45</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>10</v>
@@ -2941,7 +2941,7 @@
         <v>45</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>10</v>
@@ -2973,7 +2973,7 @@
         <v>45</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -3005,7 +3005,7 @@
         <v>45</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -3037,7 +3037,7 @@
         <v>45</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -3069,7 +3069,7 @@
         <v>45</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -3101,7 +3101,7 @@
         <v>45</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -3133,7 +3133,7 @@
         <v>45</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -3165,7 +3165,7 @@
         <v>45</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -3197,7 +3197,7 @@
         <v>45</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -3229,7 +3229,7 @@
         <v>45</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3261,7 +3261,7 @@
         <v>45</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -3293,7 +3293,7 @@
         <v>45</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3325,7 +3325,7 @@
         <v>45</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -3357,7 +3357,7 @@
         <v>45</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3389,7 +3389,7 @@
         <v>45</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3421,7 +3421,7 @@
         <v>45</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>13</v>
@@ -3453,7 +3453,7 @@
         <v>45</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3485,7 +3485,7 @@
         <v>45</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3517,7 +3517,7 @@
         <v>45</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3549,7 +3549,7 @@
         <v>45</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3581,7 +3581,7 @@
         <v>45</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3613,7 +3613,7 @@
         <v>45</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3645,7 +3645,7 @@
         <v>45</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -3677,7 +3677,7 @@
         <v>45</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>10</v>
@@ -3709,7 +3709,7 @@
         <v>45</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>10</v>
@@ -3741,7 +3741,7 @@
         <v>45</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3773,7 +3773,7 @@
         <v>45</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3805,7 +3805,7 @@
         <v>45</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3837,7 +3837,7 @@
         <v>45</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3869,7 +3869,7 @@
         <v>45</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3901,7 +3901,7 @@
         <v>45</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>10</v>
@@ -3933,7 +3933,7 @@
         <v>45</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3965,7 +3965,7 @@
         <v>45</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3997,7 +3997,7 @@
         <v>45</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -4029,7 +4029,7 @@
         <v>45</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>10</v>
@@ -4061,7 +4061,7 @@
         <v>45</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>10</v>
@@ -4093,7 +4093,7 @@
         <v>45</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -4125,7 +4125,7 @@
         <v>45</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -4157,7 +4157,7 @@
         <v>45</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>10</v>
@@ -4189,7 +4189,7 @@
         <v>45</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>45</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -5309,7 +5309,7 @@
         <v>45</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>10</v>
@@ -5341,7 +5341,7 @@
         <v>45</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>10</v>
@@ -5373,7 +5373,7 @@
         <v>45</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>10</v>
@@ -5405,7 +5405,7 @@
         <v>45</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>10</v>
@@ -5437,7 +5437,7 @@
         <v>45</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>10</v>
@@ -5469,7 +5469,7 @@
         <v>45</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>10</v>
@@ -5501,7 +5501,7 @@
         <v>45</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>10</v>
@@ -5533,7 +5533,7 @@
         <v>45</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>10</v>
@@ -5565,7 +5565,7 @@
         <v>45</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>10</v>
@@ -5597,7 +5597,7 @@
         <v>45</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>10</v>
@@ -5629,7 +5629,7 @@
         <v>45</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>10</v>
@@ -5661,7 +5661,7 @@
         <v>45</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>10</v>
@@ -5693,7 +5693,7 @@
         <v>45</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>10</v>
@@ -5725,7 +5725,7 @@
         <v>45</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>10</v>
@@ -5757,7 +5757,7 @@
         <v>45</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>10</v>
@@ -5789,7 +5789,7 @@
         <v>45</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>10</v>
@@ -5821,7 +5821,7 @@
         <v>45</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>10</v>
@@ -5853,7 +5853,7 @@
         <v>45</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>10</v>
@@ -5885,7 +5885,7 @@
         <v>45</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>10</v>
@@ -5917,7 +5917,7 @@
         <v>45</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5949,7 +5949,7 @@
         <v>45</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>10</v>
@@ -5981,7 +5981,7 @@
         <v>45</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>13</v>
@@ -6013,7 +6013,7 @@
         <v>45</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -6045,7 +6045,7 @@
         <v>45</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>10</v>
@@ -6077,7 +6077,7 @@
         <v>45</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>10</v>
@@ -6109,7 +6109,7 @@
         <v>45</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -6141,7 +6141,7 @@
         <v>45</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>13</v>
@@ -6173,7 +6173,7 @@
         <v>45</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>10</v>
@@ -6205,7 +6205,7 @@
         <v>45</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>10</v>
@@ -6237,7 +6237,7 @@
         <v>45</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>10</v>
@@ -6269,7 +6269,7 @@
         <v>45</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>10</v>
@@ -6301,7 +6301,7 @@
         <v>45</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>10</v>
@@ -6333,7 +6333,7 @@
         <v>45</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>10</v>
@@ -6365,7 +6365,7 @@
         <v>45</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>10</v>
@@ -6397,7 +6397,7 @@
         <v>45</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>10</v>
@@ -6429,7 +6429,7 @@
         <v>45</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>10</v>
@@ -6461,7 +6461,7 @@
         <v>45</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -6493,7 +6493,7 @@
         <v>45</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>10</v>
@@ -6525,7 +6525,7 @@
         <v>45</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>10</v>
@@ -6557,7 +6557,7 @@
         <v>45</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>10</v>
@@ -6589,7 +6589,7 @@
         <v>45</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>10</v>
@@ -6621,7 +6621,7 @@
         <v>45</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -6653,7 +6653,7 @@
         <v>45</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -6685,7 +6685,7 @@
         <v>45</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>10</v>
@@ -6717,7 +6717,7 @@
         <v>45</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>10</v>
@@ -6749,7 +6749,7 @@
         <v>45</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>10</v>
@@ -6781,7 +6781,7 @@
         <v>45</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>10</v>
@@ -6813,7 +6813,7 @@
         <v>45</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>10</v>
@@ -6845,7 +6845,7 @@
         <v>45</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>10</v>
@@ -6877,7 +6877,7 @@
         <v>45</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>10</v>
@@ -6909,7 +6909,7 @@
         <v>45</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>10</v>
@@ -6941,7 +6941,7 @@
         <v>45</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>10</v>
@@ -6973,7 +6973,7 @@
         <v>45</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>10</v>
@@ -7005,7 +7005,7 @@
         <v>45</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>10</v>
@@ -7037,7 +7037,7 @@
         <v>45</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>10</v>
@@ -7069,7 +7069,7 @@
         <v>45</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>10</v>
@@ -7101,7 +7101,7 @@
         <v>45</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>10</v>
@@ -7133,7 +7133,7 @@
         <v>45</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>12</v>
@@ -7157,7 +7157,7 @@
       <c r="J211" s="2"/>
       <c r="K211" s="1"/>
       <c r="M211" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="212" spans="4:13" x14ac:dyDescent="0.3">
@@ -7174,7 +7174,7 @@
         <v>45</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -7206,7 +7206,7 @@
         <v>45</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>10</v>
@@ -7238,7 +7238,7 @@
         <v>45</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -7270,7 +7270,7 @@
         <v>45</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -7654,7 +7654,7 @@
         <v>45</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>10</v>
@@ -7686,7 +7686,7 @@
         <v>45</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>10</v>
@@ -7718,7 +7718,7 @@
         <v>45</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -7750,7 +7750,7 @@
         <v>45</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -7782,7 +7782,7 @@
         <v>45</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>10</v>
@@ -7814,7 +7814,7 @@
         <v>45</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>10</v>
@@ -7846,7 +7846,7 @@
         <v>45</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>10</v>
@@ -7878,7 +7878,7 @@
         <v>45</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>10</v>
@@ -7910,7 +7910,7 @@
         <v>45</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>10</v>
@@ -7942,7 +7942,7 @@
         <v>45</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>10</v>
@@ -7974,7 +7974,7 @@
         <v>45</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -8006,7 +8006,7 @@
         <v>45</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -8038,7 +8038,7 @@
         <v>45</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>10</v>
@@ -8070,7 +8070,7 @@
         <v>45</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>10</v>
@@ -8102,7 +8102,7 @@
         <v>45</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>10</v>
@@ -8134,7 +8134,7 @@
         <v>45</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>10</v>
@@ -8166,7 +8166,7 @@
         <v>45</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>10</v>
@@ -8198,7 +8198,7 @@
         <v>45</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>45</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>10</v>
@@ -8262,7 +8262,7 @@
         <v>45</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>10</v>
@@ -8294,7 +8294,7 @@
         <v>45</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -8326,7 +8326,7 @@
         <v>45</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -8358,7 +8358,7 @@
         <v>45</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>13</v>
@@ -8390,7 +8390,7 @@
         <v>45</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>10</v>
@@ -8422,7 +8422,7 @@
         <v>45</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>10</v>
@@ -8454,7 +8454,7 @@
         <v>45</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>10</v>
@@ -8486,7 +8486,7 @@
         <v>45</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>10</v>
@@ -8518,7 +8518,7 @@
         <v>45</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -8550,7 +8550,7 @@
         <v>45</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -8582,7 +8582,7 @@
         <v>45</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>10</v>
@@ -8614,7 +8614,7 @@
         <v>45</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -8646,7 +8646,7 @@
         <v>45</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>10</v>
@@ -8678,7 +8678,7 @@
         <v>45</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -8710,7 +8710,7 @@
         <v>45</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>10</v>
@@ -8742,7 +8742,7 @@
         <v>45</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -8774,7 +8774,7 @@
         <v>45</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>10</v>
@@ -8806,7 +8806,7 @@
         <v>45</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>10</v>
@@ -8838,7 +8838,7 @@
         <v>45</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -8870,7 +8870,7 @@
         <v>45</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>10</v>
@@ -8902,7 +8902,7 @@
         <v>45</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -8934,7 +8934,7 @@
         <v>45</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>10</v>
@@ -8966,7 +8966,7 @@
         <v>45</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>10</v>
@@ -8998,7 +8998,7 @@
         <v>45</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>10</v>
@@ -9030,7 +9030,7 @@
         <v>45</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>10</v>
@@ -9062,7 +9062,7 @@
         <v>45</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>10</v>
@@ -9094,7 +9094,7 @@
         <v>45</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>10</v>
@@ -9126,7 +9126,7 @@
         <v>45</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>10</v>
@@ -9158,7 +9158,7 @@
         <v>45</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>10</v>
@@ -9190,7 +9190,7 @@
         <v>45</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>10</v>
@@ -9222,7 +9222,7 @@
         <v>45</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>10</v>
@@ -9254,7 +9254,7 @@
         <v>45</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>10</v>
@@ -9286,7 +9286,7 @@
         <v>45</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>10</v>
@@ -9318,7 +9318,7 @@
         <v>45</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>10</v>
@@ -9350,7 +9350,7 @@
         <v>45</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>10</v>
@@ -9382,7 +9382,7 @@
         <v>45</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -9414,7 +9414,7 @@
         <v>45</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>13</v>
@@ -9446,7 +9446,7 @@
         <v>45</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>12</v>
@@ -9470,7 +9470,7 @@
       <c r="J284" s="2"/>
       <c r="K284" s="1"/>
       <c r="M284" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="285" spans="4:13" x14ac:dyDescent="0.3">
@@ -9487,7 +9487,7 @@
         <v>45</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>10</v>
@@ -9519,7 +9519,7 @@
         <v>45</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>12</v>
@@ -9543,7 +9543,7 @@
       <c r="J287" s="2"/>
       <c r="K287" s="1"/>
       <c r="M287" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="288" spans="4:13" x14ac:dyDescent="0.3">
@@ -9560,7 +9560,7 @@
         <v>45</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>10</v>
@@ -9592,7 +9592,7 @@
         <v>45</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>10</v>
@@ -9624,7 +9624,7 @@
         <v>45</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>10</v>
@@ -9656,7 +9656,7 @@
         <v>45</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>10</v>
@@ -9688,7 +9688,7 @@
         <v>45</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>12</v>
@@ -9712,7 +9712,7 @@
       <c r="J293" s="2"/>
       <c r="K293" s="1"/>
       <c r="M293" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="294" spans="4:13" x14ac:dyDescent="0.3">
@@ -9729,7 +9729,7 @@
         <v>45</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -9761,7 +9761,7 @@
         <v>45</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>12</v>
@@ -9785,7 +9785,7 @@
       <c r="J296" s="2"/>
       <c r="K296" s="1"/>
       <c r="M296" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="297" spans="4:13" x14ac:dyDescent="0.3">
@@ -9802,7 +9802,7 @@
         <v>45</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>13</v>
@@ -9834,7 +9834,7 @@
         <v>45</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>10</v>
@@ -9866,7 +9866,7 @@
         <v>45</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>10</v>
@@ -9898,7 +9898,7 @@
         <v>45</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>10</v>
@@ -9930,7 +9930,7 @@
         <v>45</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>10</v>
@@ -9962,7 +9962,7 @@
         <v>45</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>10</v>
@@ -9994,7 +9994,7 @@
         <v>45</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>10</v>
@@ -10026,7 +10026,7 @@
         <v>45</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>10</v>
@@ -10058,7 +10058,7 @@
         <v>45</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>10</v>
@@ -10090,7 +10090,7 @@
         <v>45</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -10122,7 +10122,7 @@
         <v>45</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>10</v>
@@ -10154,7 +10154,7 @@
         <v>45</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>10</v>
@@ -10186,13 +10186,13 @@
         <v>45</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J309" s="2">
-        <v>0</v>
+        <v>7.9745370370370369E-3</v>
       </c>
       <c r="K309" s="1">
         <v>46176.470370370371</v>
@@ -10218,7 +10218,7 @@
         <v>45</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>10</v>
@@ -10250,7 +10250,7 @@
         <v>45</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>10</v>
@@ -10282,7 +10282,7 @@
         <v>45</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>10</v>
@@ -10314,7 +10314,7 @@
         <v>45</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>10</v>
@@ -10346,13 +10346,13 @@
         <v>45</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J314" s="2">
-        <v>8.3912037037037045E-3</v>
+        <v>8.4375000000000006E-3</v>
       </c>
       <c r="K314" s="1">
         <v>46176.471759259257</v>
@@ -10378,7 +10378,7 @@
         <v>45</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>10</v>
@@ -10410,7 +10410,7 @@
         <v>45</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>10</v>
@@ -10442,7 +10442,7 @@
         <v>45</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>10</v>
@@ -10474,7 +10474,7 @@
         <v>45</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>10</v>
@@ -10493,108 +10493,394 @@
       </c>
     </row>
     <row r="319" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H319" s="2"/>
-      <c r="I319" s="1"/>
-      <c r="J319" s="2"/>
-      <c r="K319" s="1"/>
+      <c r="D319" t="s">
+        <v>43</v>
+      </c>
+      <c r="E319">
+        <v>2067</v>
+      </c>
+      <c r="F319" t="s">
+        <v>55</v>
+      </c>
+      <c r="G319" t="s">
+        <v>45</v>
+      </c>
+      <c r="H319" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I319" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J319" s="2">
+        <v>0</v>
+      </c>
+      <c r="K319" s="1">
+        <v>46219.680555555555</v>
+      </c>
+      <c r="L319">
+        <v>0</v>
+      </c>
+      <c r="M319" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="320" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H320" s="2"/>
-      <c r="I320" s="1"/>
-      <c r="J320" s="2"/>
-      <c r="K320" s="1"/>
-    </row>
-    <row r="321" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H321" s="2"/>
-      <c r="I321" s="1"/>
-      <c r="J321" s="2"/>
-      <c r="K321" s="1"/>
-    </row>
-    <row r="322" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H322" s="2"/>
-      <c r="I322" s="1"/>
-      <c r="J322" s="2"/>
-      <c r="K322" s="1"/>
-    </row>
-    <row r="323" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H323" s="2"/>
-      <c r="I323" s="1"/>
-      <c r="J323" s="2"/>
-      <c r="K323" s="1"/>
-    </row>
-    <row r="324" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H324" s="2"/>
-      <c r="I324" s="1"/>
-      <c r="J324" s="2"/>
-      <c r="K324" s="1"/>
-    </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H325" s="2"/>
-      <c r="I325" s="1"/>
-      <c r="J325" s="2"/>
-      <c r="K325" s="1"/>
-    </row>
-    <row r="326" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H326" s="2"/>
-      <c r="I326" s="1"/>
-      <c r="J326" s="2"/>
-      <c r="K326" s="1"/>
-    </row>
-    <row r="327" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H327" s="2"/>
-      <c r="I327" s="1"/>
-      <c r="J327" s="2"/>
-      <c r="K327" s="1"/>
-    </row>
-    <row r="328" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H328" s="2"/>
-      <c r="I328" s="1"/>
-      <c r="J328" s="2"/>
-      <c r="K328" s="1"/>
-    </row>
-    <row r="329" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H329" s="2"/>
-      <c r="I329" s="1"/>
-      <c r="J329" s="2"/>
-      <c r="K329" s="1"/>
-    </row>
-    <row r="330" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D320" t="s">
+        <v>43</v>
+      </c>
+      <c r="E320">
+        <v>1125</v>
+      </c>
+      <c r="F320" t="s">
+        <v>46</v>
+      </c>
+      <c r="G320" t="s">
+        <v>45</v>
+      </c>
+      <c r="H320" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I320" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J320" s="2">
+        <v>0</v>
+      </c>
+      <c r="K320" s="1">
+        <v>46219.680555555555</v>
+      </c>
+      <c r="L320">
+        <v>0</v>
+      </c>
+      <c r="M320" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="321" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D321" t="s">
+        <v>43</v>
+      </c>
+      <c r="E321">
+        <v>1126</v>
+      </c>
+      <c r="F321" t="s">
+        <v>48</v>
+      </c>
+      <c r="G321" t="s">
+        <v>45</v>
+      </c>
+      <c r="H321" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I321" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J321" s="2">
+        <v>0</v>
+      </c>
+      <c r="K321" s="1">
+        <v>46219.681250000001</v>
+      </c>
+      <c r="L321">
+        <v>0</v>
+      </c>
+      <c r="M321" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="322" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D322" t="s">
+        <v>43</v>
+      </c>
+      <c r="E322">
+        <v>1128</v>
+      </c>
+      <c r="F322" t="s">
+        <v>49</v>
+      </c>
+      <c r="G322" t="s">
+        <v>45</v>
+      </c>
+      <c r="H322" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I322" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J322" s="2">
+        <v>0</v>
+      </c>
+      <c r="K322" s="1">
+        <v>46219.681944444441</v>
+      </c>
+      <c r="L322">
+        <v>0</v>
+      </c>
+      <c r="M322" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="323" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D323" t="s">
+        <v>43</v>
+      </c>
+      <c r="E323">
+        <v>914</v>
+      </c>
+      <c r="F323" t="s">
+        <v>50</v>
+      </c>
+      <c r="G323" t="s">
+        <v>45</v>
+      </c>
+      <c r="H323" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I323" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J323" s="2">
+        <v>6.5740740740740742E-3</v>
+      </c>
+      <c r="K323" s="1">
+        <v>46219.681944444441</v>
+      </c>
+      <c r="L323">
+        <v>0</v>
+      </c>
+      <c r="M323" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="324" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D324" t="s">
+        <v>43</v>
+      </c>
+      <c r="E324">
+        <v>1130</v>
+      </c>
+      <c r="F324" t="s">
+        <v>51</v>
+      </c>
+      <c r="G324" t="s">
+        <v>45</v>
+      </c>
+      <c r="H324" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I324" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J324" s="2">
+        <v>0</v>
+      </c>
+      <c r="K324" s="1">
+        <v>46219.682638888888</v>
+      </c>
+      <c r="L324">
+        <v>0</v>
+      </c>
+      <c r="M324" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="325" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D325" t="s">
+        <v>43</v>
+      </c>
+      <c r="E325">
+        <v>1129</v>
+      </c>
+      <c r="F325" t="s">
+        <v>52</v>
+      </c>
+      <c r="G325" t="s">
+        <v>45</v>
+      </c>
+      <c r="H325" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I325" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J325" s="2">
+        <v>0</v>
+      </c>
+      <c r="K325" s="1">
+        <v>46219.683333333334</v>
+      </c>
+      <c r="L325">
+        <v>0</v>
+      </c>
+      <c r="M325" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="326" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D326" t="s">
+        <v>43</v>
+      </c>
+      <c r="E326">
+        <v>771</v>
+      </c>
+      <c r="F326" t="s">
+        <v>53</v>
+      </c>
+      <c r="G326" t="s">
+        <v>45</v>
+      </c>
+      <c r="H326" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I326" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J326" s="2">
+        <v>6.2152777777777779E-3</v>
+      </c>
+      <c r="K326" s="1">
+        <v>46219.683333333334</v>
+      </c>
+      <c r="L326">
+        <v>0</v>
+      </c>
+      <c r="M326" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="327" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D327" t="s">
+        <v>43</v>
+      </c>
+      <c r="E327">
+        <v>2268</v>
+      </c>
+      <c r="F327" t="s">
+        <v>45</v>
+      </c>
+      <c r="G327" t="s">
+        <v>45</v>
+      </c>
+      <c r="H327" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I327" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J327" s="2">
+        <v>7.2222222222222219E-3</v>
+      </c>
+      <c r="K327" s="1">
+        <v>46219.684027777781</v>
+      </c>
+      <c r="L327">
+        <v>0</v>
+      </c>
+      <c r="M327" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="328" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D328" t="s">
+        <v>43</v>
+      </c>
+      <c r="E328">
+        <v>4661</v>
+      </c>
+      <c r="F328" t="s">
+        <v>56</v>
+      </c>
+      <c r="G328" t="s">
+        <v>45</v>
+      </c>
+      <c r="H328" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I328" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J328" s="2">
+        <v>0</v>
+      </c>
+      <c r="K328" s="1">
+        <v>46219.68472222222</v>
+      </c>
+      <c r="L328">
+        <v>0</v>
+      </c>
+      <c r="M328" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="329" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D329" t="s">
+        <v>43</v>
+      </c>
+      <c r="E329">
+        <v>1132</v>
+      </c>
+      <c r="F329" t="s">
+        <v>54</v>
+      </c>
+      <c r="G329" t="s">
+        <v>45</v>
+      </c>
+      <c r="H329" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I329" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J329" s="2">
+        <v>6.7939814814814816E-3</v>
+      </c>
+      <c r="K329" s="1">
+        <v>46219.68472222222</v>
+      </c>
+      <c r="L329">
+        <v>0</v>
+      </c>
+      <c r="M329" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="330" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H330" s="2"/>
       <c r="I330" s="1"/>
       <c r="J330" s="2"/>
       <c r="K330" s="1"/>
     </row>
-    <row r="331" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H331" s="2"/>
       <c r="I331" s="1"/>
       <c r="J331" s="2"/>
       <c r="K331" s="1"/>
     </row>
-    <row r="332" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H332" s="2"/>
       <c r="I332" s="1"/>
       <c r="J332" s="2"/>
       <c r="K332" s="1"/>
     </row>
-    <row r="333" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H333" s="2"/>
       <c r="I333" s="1"/>
       <c r="J333" s="2"/>
       <c r="K333" s="1"/>
     </row>
-    <row r="334" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H334" s="2"/>
       <c r="I334" s="1"/>
       <c r="J334" s="2"/>
       <c r="K334" s="1"/>
     </row>
-    <row r="335" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H335" s="2"/>
       <c r="I335" s="1"/>
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -11413,6 +11699,7 @@
     <row r="472" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H472" s="2"/>
       <c r="I472" s="1"/>
+      <c r="J472" s="2"/>
       <c r="K472" s="1"/>
     </row>
     <row r="473" spans="8:11" x14ac:dyDescent="0.3">
@@ -12761,6 +13048,7 @@
     <row r="697" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H697" s="2"/>
       <c r="I697" s="1"/>
+      <c r="J697" s="2"/>
       <c r="K697" s="1"/>
     </row>
     <row r="698" spans="8:11" x14ac:dyDescent="0.3">
@@ -13070,6 +13358,7 @@
     <row r="749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H749" s="2"/>
       <c r="I749" s="1"/>
+      <c r="J749" s="2"/>
       <c r="K749" s="1"/>
     </row>
     <row r="750" spans="8:11" x14ac:dyDescent="0.3">
@@ -13159,6 +13448,7 @@
     <row r="764" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
+      <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
     <row r="765" spans="8:11" x14ac:dyDescent="0.3">
@@ -13265,6 +13555,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -13282,6 +13573,7 @@
     <row r="785" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H785" s="2"/>
       <c r="I785" s="1"/>
+      <c r="J785" s="2"/>
       <c r="K785" s="1"/>
     </row>
     <row r="786" spans="8:11" x14ac:dyDescent="0.3">
@@ -13293,6 +13585,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -13334,6 +13627,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -13357,6 +13651,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -13380,6 +13675,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -13397,6 +13693,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -13408,11 +13705,13 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -13532,6 +13831,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -13615,6 +13915,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -13638,6 +13939,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -13649,6 +13951,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -13660,6 +13963,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -13707,6 +14011,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -13760,6 +14065,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -13932,6 +14238,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -13943,6 +14250,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -14020,6 +14328,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -14037,6 +14346,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -14084,6 +14394,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -14196,6 +14507,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -14255,6 +14567,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -14266,6 +14579,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -14337,6 +14651,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -14389,6 +14704,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -14465,11 +14781,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -14529,6 +14847,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -14540,6 +14859,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -14551,11 +14871,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -14609,6 +14931,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -14625,6 +14948,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -14648,6 +14972,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -14665,6 +14990,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -14711,11 +15037,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -14757,11 +15085,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -14779,6 +15109,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -14790,6 +15121,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -14801,6 +15133,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -14818,6 +15151,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -14895,6 +15229,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -14924,6 +15259,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -14935,16 +15271,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -14956,16 +15295,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -14977,11 +15319,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -15005,6 +15349,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -15046,6 +15391,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -15075,21 +15421,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -15101,6 +15451,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -15118,6 +15469,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -15157,11 +15509,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -15209,6 +15563,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -15238,6 +15593,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -15314,6 +15670,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -15360,6 +15717,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -15395,11 +15753,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -15416,6 +15776,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -15426,6 +15787,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -15461,6 +15823,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -15472,6 +15835,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -15483,6 +15847,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -15494,6 +15859,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -15505,6 +15871,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -15546,6 +15913,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -15563,6 +15931,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -15580,6 +15949,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -15621,6 +15991,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -15644,6 +16015,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -15690,6 +16062,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -15725,6 +16098,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -15748,6 +16122,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -15788,6 +16163,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -15805,11 +16181,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -15868,6 +16246,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -15884,6 +16263,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -15895,6 +16275,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -15906,11 +16287,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -15946,6 +16329,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -15998,6 +16382,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -16008,6 +16393,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -16023,6 +16409,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -16046,16 +16433,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -16126,6 +16516,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -16137,6 +16528,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -16237,6 +16629,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -16293,6 +16687,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -16316,6 +16711,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -16440,6 +16836,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -16598,6 +16995,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -16615,6 +17013,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -16655,6 +17054,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -16987,6 +17387,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -17075,6 +17476,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -17168,6 +17570,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -17227,11 +17630,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -17283,6 +17688,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -17324,6 +17730,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -17368,6 +17775,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -17414,11 +17822,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -17616,6 +18026,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -17645,6 +18056,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -17660,6 +18073,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -17719,6 +18133,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -17790,6 +18205,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -17831,6 +18247,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -17949,6 +18366,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -18013,6 +18431,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -18137,6 +18556,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -18363,6 +18783,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -18480,6 +18901,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -18563,6 +18985,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -18622,6 +19045,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -18645,6 +19069,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -18692,6 +19117,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -18751,6 +19177,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -18774,6 +19201,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -18791,6 +19219,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -18874,6 +19303,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -19065,6 +19495,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -46921,6 +47352,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -46928,6 +47360,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -46935,6 +47368,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -46950,6 +47384,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -46959,6 +47394,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -46966,9 +47402,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -46976,12 +47418,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -46989,12 +47434,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -47006,9 +47454,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -47023,6 +47473,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -47049,6 +47500,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -47059,7 +47511,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -47067,6 +47524,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -47078,6 +47536,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -47085,6 +47544,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -47099,13 +47559,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -47116,15 +47582,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -47140,6 +47609,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -47158,6 +47628,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -47169,6 +47640,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -47186,18 +47658,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -47226,6 +47703,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -47233,9 +47711,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -47258,12 +47738,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -47278,9 +47761,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -47296,12 +47781,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -47322,6 +47809,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -47333,9 +47821,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -47347,6 +47837,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -47386,9 +47877,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -47396,9 +47889,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -47409,6 +47904,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -47416,18 +47912,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -47435,6 +47939,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -47445,6 +47950,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -47471,15 +47977,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -47501,6 +48011,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -47508,9 +48019,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -47518,6 +48031,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -47529,6 +48043,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -47543,6 +48058,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -47552,6 +48071,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -47563,6 +48083,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -47573,10 +48094,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -47584,6 +48110,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -47598,6 +48125,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -47620,6 +48148,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -47639,25 +48168,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -47665,6 +48206,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -47672,15 +48214,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -47694,6 +48243,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -47712,9 +48262,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -47722,9 +48274,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -47732,6 +48286,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -47748,10 +48303,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
